--- a/output/version3/test/15-5/MARL/IL/RL-RL/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-5/MARL/IL/RL-RL/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>569</v>
+        <v>599</v>
       </c>
       <c r="C2" t="n">
-        <v>617</v>
+        <v>585</v>
       </c>
       <c r="D2" t="n">
-        <v>590</v>
+        <v>548</v>
       </c>
       <c r="E2" t="n">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="F2" t="n">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G2" t="n">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H2" t="n">
-        <v>558</v>
+        <v>651</v>
       </c>
       <c r="I2" t="n">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="J2" t="n">
-        <v>612</v>
+        <v>638</v>
       </c>
       <c r="K2" t="n">
-        <v>578</v>
+        <v>563</v>
       </c>
       <c r="L2" t="n">
-        <v>598.7</v>
+        <v>607.5</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>760</v>
+        <v>801</v>
       </c>
       <c r="C3" t="n">
-        <v>672</v>
+        <v>893</v>
       </c>
       <c r="D3" t="n">
-        <v>822</v>
+        <v>712</v>
       </c>
       <c r="E3" t="n">
-        <v>825</v>
+        <v>733</v>
       </c>
       <c r="F3" t="n">
-        <v>740</v>
+        <v>865</v>
       </c>
       <c r="G3" t="n">
-        <v>771</v>
+        <v>823</v>
       </c>
       <c r="H3" t="n">
-        <v>774</v>
+        <v>667</v>
       </c>
       <c r="I3" t="n">
-        <v>719</v>
+        <v>755</v>
       </c>
       <c r="J3" t="n">
-        <v>680</v>
+        <v>716</v>
       </c>
       <c r="K3" t="n">
-        <v>751</v>
+        <v>725</v>
       </c>
       <c r="L3" t="n">
-        <v>751.4</v>
+        <v>769</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>746</v>
+        <v>654</v>
       </c>
       <c r="C4" t="n">
-        <v>651</v>
+        <v>600</v>
       </c>
       <c r="D4" t="n">
-        <v>739</v>
+        <v>652</v>
       </c>
       <c r="E4" t="n">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="F4" t="n">
-        <v>886</v>
+        <v>654</v>
       </c>
       <c r="G4" t="n">
-        <v>723</v>
+        <v>668</v>
       </c>
       <c r="H4" t="n">
-        <v>646</v>
+        <v>730</v>
       </c>
       <c r="I4" t="n">
-        <v>689</v>
+        <v>667</v>
       </c>
       <c r="J4" t="n">
-        <v>774</v>
+        <v>681</v>
       </c>
       <c r="K4" t="n">
-        <v>706</v>
+        <v>751</v>
       </c>
       <c r="L4" t="n">
-        <v>721.1</v>
+        <v>675.3</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>889</v>
+        <v>860</v>
       </c>
       <c r="C5" t="n">
-        <v>829</v>
+        <v>789</v>
       </c>
       <c r="D5" t="n">
-        <v>787</v>
+        <v>857</v>
       </c>
       <c r="E5" t="n">
-        <v>782</v>
+        <v>897</v>
       </c>
       <c r="F5" t="n">
-        <v>807</v>
+        <v>917</v>
       </c>
       <c r="G5" t="n">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="H5" t="n">
-        <v>864</v>
+        <v>928</v>
       </c>
       <c r="I5" t="n">
-        <v>770</v>
+        <v>819</v>
       </c>
       <c r="J5" t="n">
-        <v>820</v>
+        <v>777</v>
       </c>
       <c r="K5" t="n">
-        <v>846</v>
+        <v>768</v>
       </c>
       <c r="L5" t="n">
-        <v>824.6</v>
+        <v>845.6</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>666</v>
+        <v>595</v>
       </c>
       <c r="C6" t="n">
-        <v>668</v>
+        <v>623</v>
       </c>
       <c r="D6" t="n">
-        <v>676</v>
+        <v>575</v>
       </c>
       <c r="E6" t="n">
-        <v>609</v>
+        <v>627</v>
       </c>
       <c r="F6" t="n">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G6" t="n">
-        <v>627</v>
+        <v>671</v>
       </c>
       <c r="H6" t="n">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="I6" t="n">
-        <v>717</v>
+        <v>689</v>
       </c>
       <c r="J6" t="n">
-        <v>651</v>
+        <v>702</v>
       </c>
       <c r="K6" t="n">
-        <v>658</v>
+        <v>623</v>
       </c>
       <c r="L6" t="n">
-        <v>652.3</v>
+        <v>635.6</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>841</v>
+        <v>764</v>
       </c>
       <c r="C7" t="n">
-        <v>782</v>
+        <v>826</v>
       </c>
       <c r="D7" t="n">
-        <v>719</v>
+        <v>767</v>
       </c>
       <c r="E7" t="n">
-        <v>852</v>
+        <v>748</v>
       </c>
       <c r="F7" t="n">
-        <v>751</v>
+        <v>861</v>
       </c>
       <c r="G7" t="n">
-        <v>689</v>
+        <v>716</v>
       </c>
       <c r="H7" t="n">
-        <v>769</v>
+        <v>744</v>
       </c>
       <c r="I7" t="n">
-        <v>757</v>
+        <v>808</v>
       </c>
       <c r="J7" t="n">
-        <v>729</v>
+        <v>681</v>
       </c>
       <c r="K7" t="n">
-        <v>804</v>
+        <v>783</v>
       </c>
       <c r="L7" t="n">
-        <v>769.3</v>
+        <v>769.8</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>743</v>
+        <v>694</v>
       </c>
       <c r="C8" t="n">
-        <v>670</v>
+        <v>644</v>
       </c>
       <c r="D8" t="n">
-        <v>686</v>
+        <v>654</v>
       </c>
       <c r="E8" t="n">
-        <v>627</v>
+        <v>731</v>
       </c>
       <c r="F8" t="n">
-        <v>684</v>
+        <v>800</v>
       </c>
       <c r="G8" t="n">
-        <v>666</v>
+        <v>642</v>
       </c>
       <c r="H8" t="n">
-        <v>624</v>
+        <v>584</v>
       </c>
       <c r="I8" t="n">
-        <v>710</v>
+        <v>656</v>
       </c>
       <c r="J8" t="n">
-        <v>620</v>
+        <v>655</v>
       </c>
       <c r="K8" t="n">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="L8" t="n">
-        <v>665.4</v>
+        <v>667</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>562</v>
+        <v>616</v>
       </c>
       <c r="C9" t="n">
-        <v>630</v>
+        <v>644</v>
       </c>
       <c r="D9" t="n">
-        <v>622</v>
+        <v>691</v>
       </c>
       <c r="E9" t="n">
-        <v>561</v>
+        <v>645</v>
       </c>
       <c r="F9" t="n">
-        <v>596</v>
+        <v>637</v>
       </c>
       <c r="G9" t="n">
-        <v>626</v>
+        <v>574</v>
       </c>
       <c r="H9" t="n">
-        <v>678</v>
+        <v>576</v>
       </c>
       <c r="I9" t="n">
-        <v>749</v>
+        <v>711</v>
       </c>
       <c r="J9" t="n">
-        <v>676</v>
+        <v>707</v>
       </c>
       <c r="K9" t="n">
-        <v>606</v>
+        <v>686</v>
       </c>
       <c r="L9" t="n">
-        <v>630.6</v>
+        <v>648.7</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>876</v>
+        <v>785</v>
       </c>
       <c r="C10" t="n">
-        <v>805</v>
+        <v>705</v>
       </c>
       <c r="D10" t="n">
-        <v>816</v>
+        <v>757</v>
       </c>
       <c r="E10" t="n">
-        <v>794</v>
+        <v>741</v>
       </c>
       <c r="F10" t="n">
-        <v>839</v>
+        <v>747</v>
       </c>
       <c r="G10" t="n">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="H10" t="n">
-        <v>698</v>
+        <v>743</v>
       </c>
       <c r="I10" t="n">
-        <v>732</v>
+        <v>818</v>
       </c>
       <c r="J10" t="n">
-        <v>690</v>
+        <v>817</v>
       </c>
       <c r="K10" t="n">
-        <v>842</v>
+        <v>734</v>
       </c>
       <c r="L10" t="n">
-        <v>786</v>
+        <v>761.2</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>713</v>
+        <v>800</v>
       </c>
       <c r="C11" t="n">
-        <v>849</v>
+        <v>672</v>
       </c>
       <c r="D11" t="n">
-        <v>768</v>
+        <v>714</v>
       </c>
       <c r="E11" t="n">
-        <v>787</v>
+        <v>739</v>
       </c>
       <c r="F11" t="n">
-        <v>743</v>
+        <v>759</v>
       </c>
       <c r="G11" t="n">
-        <v>716</v>
+        <v>744</v>
       </c>
       <c r="H11" t="n">
-        <v>771</v>
+        <v>790</v>
       </c>
       <c r="I11" t="n">
-        <v>688</v>
+        <v>742</v>
       </c>
       <c r="J11" t="n">
-        <v>722</v>
+        <v>697</v>
       </c>
       <c r="K11" t="n">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="L11" t="n">
-        <v>753.9</v>
+        <v>742.9</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>676</v>
+        <v>657</v>
       </c>
       <c r="C12" t="n">
-        <v>694</v>
+        <v>670</v>
       </c>
       <c r="D12" t="n">
-        <v>665</v>
+        <v>753</v>
       </c>
       <c r="E12" t="n">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="F12" t="n">
-        <v>706</v>
+        <v>617</v>
       </c>
       <c r="G12" t="n">
-        <v>787</v>
+        <v>732</v>
       </c>
       <c r="H12" t="n">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="I12" t="n">
-        <v>704</v>
+        <v>663</v>
       </c>
       <c r="J12" t="n">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="K12" t="n">
-        <v>669</v>
+        <v>728</v>
       </c>
       <c r="L12" t="n">
-        <v>690.5</v>
+        <v>680.7</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="C13" t="n">
-        <v>534</v>
+        <v>577</v>
       </c>
       <c r="D13" t="n">
-        <v>596</v>
+        <v>550</v>
       </c>
       <c r="E13" t="n">
-        <v>656</v>
+        <v>510</v>
       </c>
       <c r="F13" t="n">
+        <v>587</v>
+      </c>
+      <c r="G13" t="n">
+        <v>608</v>
+      </c>
+      <c r="H13" t="n">
+        <v>575</v>
+      </c>
+      <c r="I13" t="n">
+        <v>541</v>
+      </c>
+      <c r="J13" t="n">
         <v>582</v>
       </c>
-      <c r="G13" t="n">
-        <v>547</v>
-      </c>
-      <c r="H13" t="n">
-        <v>615</v>
-      </c>
-      <c r="I13" t="n">
-        <v>609</v>
-      </c>
-      <c r="J13" t="n">
-        <v>564</v>
-      </c>
       <c r="K13" t="n">
-        <v>654</v>
+        <v>606</v>
       </c>
       <c r="L13" t="n">
-        <v>598.8</v>
+        <v>575.2</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C14" t="n">
-        <v>678</v>
+        <v>610</v>
       </c>
       <c r="D14" t="n">
-        <v>620</v>
+        <v>663</v>
       </c>
       <c r="E14" t="n">
-        <v>644</v>
+        <v>615</v>
       </c>
       <c r="F14" t="n">
-        <v>636</v>
+        <v>617</v>
       </c>
       <c r="G14" t="n">
-        <v>565</v>
+        <v>609</v>
       </c>
       <c r="H14" t="n">
-        <v>669</v>
+        <v>640</v>
       </c>
       <c r="I14" t="n">
-        <v>735</v>
+        <v>543</v>
       </c>
       <c r="J14" t="n">
-        <v>623</v>
+        <v>655</v>
       </c>
       <c r="K14" t="n">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="L14" t="n">
-        <v>636.7</v>
+        <v>616</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>861</v>
+        <v>748</v>
       </c>
       <c r="C15" t="n">
-        <v>758</v>
+        <v>814</v>
       </c>
       <c r="D15" t="n">
-        <v>782</v>
+        <v>712</v>
       </c>
       <c r="E15" t="n">
-        <v>693</v>
+        <v>755</v>
       </c>
       <c r="F15" t="n">
-        <v>710</v>
+        <v>748</v>
       </c>
       <c r="G15" t="n">
-        <v>753</v>
+        <v>795</v>
       </c>
       <c r="H15" t="n">
-        <v>817</v>
+        <v>704</v>
       </c>
       <c r="I15" t="n">
-        <v>697</v>
+        <v>721</v>
       </c>
       <c r="J15" t="n">
-        <v>742</v>
+        <v>805</v>
       </c>
       <c r="K15" t="n">
-        <v>681</v>
+        <v>794</v>
       </c>
       <c r="L15" t="n">
-        <v>749.4</v>
+        <v>759.6</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>743</v>
+        <v>705</v>
       </c>
       <c r="C16" t="n">
-        <v>666</v>
+        <v>713</v>
       </c>
       <c r="D16" t="n">
-        <v>692</v>
+        <v>635</v>
       </c>
       <c r="E16" t="n">
-        <v>727</v>
+        <v>661</v>
       </c>
       <c r="F16" t="n">
-        <v>710</v>
+        <v>768</v>
       </c>
       <c r="G16" t="n">
-        <v>726</v>
+        <v>667</v>
       </c>
       <c r="H16" t="n">
-        <v>739</v>
+        <v>722</v>
       </c>
       <c r="I16" t="n">
-        <v>736</v>
+        <v>717</v>
       </c>
       <c r="J16" t="n">
-        <v>769</v>
+        <v>742</v>
       </c>
       <c r="K16" t="n">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="L16" t="n">
-        <v>716</v>
+        <v>700</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>899</v>
+        <v>785</v>
       </c>
       <c r="C17" t="n">
-        <v>808</v>
+        <v>771</v>
       </c>
       <c r="D17" t="n">
-        <v>665</v>
+        <v>855</v>
       </c>
       <c r="E17" t="n">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="F17" t="n">
-        <v>886</v>
+        <v>792</v>
       </c>
       <c r="G17" t="n">
-        <v>728</v>
+        <v>829</v>
       </c>
       <c r="H17" t="n">
-        <v>701</v>
+        <v>832</v>
       </c>
       <c r="I17" t="n">
-        <v>801</v>
+        <v>844</v>
       </c>
       <c r="J17" t="n">
-        <v>821</v>
+        <v>736</v>
       </c>
       <c r="K17" t="n">
-        <v>710</v>
+        <v>813</v>
       </c>
       <c r="L17" t="n">
-        <v>779.5</v>
+        <v>802.4</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="C18" t="n">
-        <v>766</v>
+        <v>640</v>
       </c>
       <c r="D18" t="n">
-        <v>621</v>
+        <v>648</v>
       </c>
       <c r="E18" t="n">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="F18" t="n">
-        <v>648</v>
+        <v>670</v>
       </c>
       <c r="G18" t="n">
-        <v>692</v>
+        <v>652</v>
       </c>
       <c r="H18" t="n">
-        <v>781</v>
+        <v>705</v>
       </c>
       <c r="I18" t="n">
-        <v>690</v>
+        <v>636</v>
       </c>
       <c r="J18" t="n">
-        <v>745</v>
+        <v>677</v>
       </c>
       <c r="K18" t="n">
-        <v>689</v>
+        <v>655</v>
       </c>
       <c r="L18" t="n">
-        <v>683</v>
+        <v>647.5</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>675</v>
+        <v>784</v>
       </c>
       <c r="C19" t="n">
-        <v>645</v>
+        <v>729</v>
       </c>
       <c r="D19" t="n">
-        <v>693</v>
+        <v>644</v>
       </c>
       <c r="E19" t="n">
-        <v>673</v>
+        <v>716</v>
       </c>
       <c r="F19" t="n">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G19" t="n">
-        <v>678</v>
+        <v>709</v>
       </c>
       <c r="H19" t="n">
-        <v>633</v>
+        <v>646</v>
       </c>
       <c r="I19" t="n">
+        <v>610</v>
+      </c>
+      <c r="J19" t="n">
+        <v>733</v>
+      </c>
+      <c r="K19" t="n">
         <v>705</v>
       </c>
-      <c r="J19" t="n">
-        <v>629</v>
-      </c>
-      <c r="K19" t="n">
-        <v>681</v>
-      </c>
       <c r="L19" t="n">
-        <v>671.6</v>
+        <v>697.9</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>671</v>
+        <v>597</v>
       </c>
       <c r="C20" t="n">
-        <v>694</v>
+        <v>609</v>
       </c>
       <c r="D20" t="n">
-        <v>649</v>
+        <v>676</v>
       </c>
       <c r="E20" t="n">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="F20" t="n">
-        <v>620</v>
+        <v>727</v>
       </c>
       <c r="G20" t="n">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="H20" t="n">
-        <v>664</v>
+        <v>723</v>
       </c>
       <c r="I20" t="n">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="J20" t="n">
-        <v>752</v>
+        <v>658</v>
       </c>
       <c r="K20" t="n">
-        <v>669</v>
+        <v>556</v>
       </c>
       <c r="L20" t="n">
-        <v>675.5</v>
+        <v>658.8</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>680</v>
+        <v>659</v>
       </c>
       <c r="C21" t="n">
-        <v>661</v>
+        <v>568</v>
       </c>
       <c r="D21" t="n">
-        <v>690</v>
+        <v>654</v>
       </c>
       <c r="E21" t="n">
-        <v>650</v>
+        <v>758</v>
       </c>
       <c r="F21" t="n">
-        <v>697</v>
+        <v>594</v>
       </c>
       <c r="G21" t="n">
-        <v>667</v>
+        <v>755</v>
       </c>
       <c r="H21" t="n">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="I21" t="n">
-        <v>711</v>
+        <v>666</v>
       </c>
       <c r="J21" t="n">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="K21" t="n">
-        <v>672</v>
+        <v>723</v>
       </c>
       <c r="L21" t="n">
-        <v>675.6</v>
+        <v>668.4</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>583</v>
+        <v>678</v>
       </c>
       <c r="C22" t="n">
-        <v>570</v>
+        <v>617</v>
       </c>
       <c r="D22" t="n">
-        <v>645</v>
+        <v>533</v>
       </c>
       <c r="E22" t="n">
-        <v>523</v>
+        <v>591</v>
       </c>
       <c r="F22" t="n">
-        <v>607</v>
+        <v>530</v>
       </c>
       <c r="G22" t="n">
-        <v>557</v>
+        <v>592</v>
       </c>
       <c r="H22" t="n">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="I22" t="n">
-        <v>553</v>
+        <v>671</v>
       </c>
       <c r="J22" t="n">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="K22" t="n">
-        <v>649</v>
+        <v>597</v>
       </c>
       <c r="L22" t="n">
-        <v>581.1</v>
+        <v>594.6</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>715</v>
+        <v>672</v>
       </c>
       <c r="C23" t="n">
-        <v>785</v>
+        <v>644</v>
       </c>
       <c r="D23" t="n">
-        <v>656</v>
+        <v>741</v>
       </c>
       <c r="E23" t="n">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="F23" t="n">
-        <v>740</v>
+        <v>723</v>
       </c>
       <c r="G23" t="n">
-        <v>683</v>
+        <v>699</v>
       </c>
       <c r="H23" t="n">
-        <v>694</v>
+        <v>626</v>
       </c>
       <c r="I23" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="J23" t="n">
-        <v>715</v>
+        <v>747</v>
       </c>
       <c r="K23" t="n">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="L23" t="n">
-        <v>711.5</v>
+        <v>697.3</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>692</v>
+        <v>725</v>
       </c>
       <c r="C24" t="n">
-        <v>752</v>
+        <v>616</v>
       </c>
       <c r="D24" t="n">
-        <v>734</v>
+        <v>774</v>
       </c>
       <c r="E24" t="n">
-        <v>737</v>
+        <v>780</v>
       </c>
       <c r="F24" t="n">
-        <v>693</v>
+        <v>664</v>
       </c>
       <c r="G24" t="n">
-        <v>693</v>
+        <v>749</v>
       </c>
       <c r="H24" t="n">
-        <v>691</v>
+        <v>666</v>
       </c>
       <c r="I24" t="n">
-        <v>698</v>
+        <v>715</v>
       </c>
       <c r="J24" t="n">
-        <v>749</v>
+        <v>685</v>
       </c>
       <c r="K24" t="n">
-        <v>681</v>
+        <v>621</v>
       </c>
       <c r="L24" t="n">
-        <v>712</v>
+        <v>699.5</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>747</v>
+        <v>629</v>
       </c>
       <c r="C25" t="n">
+        <v>586</v>
+      </c>
+      <c r="D25" t="n">
+        <v>685</v>
+      </c>
+      <c r="E25" t="n">
+        <v>783</v>
+      </c>
+      <c r="F25" t="n">
+        <v>634</v>
+      </c>
+      <c r="G25" t="n">
         <v>623</v>
       </c>
-      <c r="D25" t="n">
-        <v>686</v>
-      </c>
-      <c r="E25" t="n">
-        <v>653</v>
-      </c>
-      <c r="F25" t="n">
-        <v>661</v>
-      </c>
-      <c r="G25" t="n">
-        <v>616</v>
-      </c>
       <c r="H25" t="n">
-        <v>679</v>
+        <v>655</v>
       </c>
       <c r="I25" t="n">
-        <v>631</v>
+        <v>721</v>
       </c>
       <c r="J25" t="n">
-        <v>676</v>
+        <v>777</v>
       </c>
       <c r="K25" t="n">
-        <v>635</v>
+        <v>696</v>
       </c>
       <c r="L25" t="n">
-        <v>660.7</v>
+        <v>678.9</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>764</v>
+        <v>713</v>
       </c>
       <c r="C26" t="n">
-        <v>714</v>
+        <v>802</v>
       </c>
       <c r="D26" t="n">
-        <v>660</v>
+        <v>692</v>
       </c>
       <c r="E26" t="n">
         <v>702</v>
       </c>
       <c r="F26" t="n">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="G26" t="n">
-        <v>797</v>
+        <v>812</v>
       </c>
       <c r="H26" t="n">
-        <v>768</v>
+        <v>734</v>
       </c>
       <c r="I26" t="n">
-        <v>782</v>
+        <v>688</v>
       </c>
       <c r="J26" t="n">
         <v>751</v>
       </c>
       <c r="K26" t="n">
-        <v>780</v>
+        <v>670</v>
       </c>
       <c r="L26" t="n">
-        <v>747.8</v>
+        <v>732.8</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>787</v>
+        <v>738</v>
       </c>
       <c r="C27" t="n">
-        <v>712</v>
+        <v>765</v>
       </c>
       <c r="D27" t="n">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="E27" t="n">
-        <v>764</v>
+        <v>694</v>
       </c>
       <c r="F27" t="n">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="G27" t="n">
-        <v>757</v>
+        <v>803</v>
       </c>
       <c r="H27" t="n">
-        <v>731</v>
+        <v>684</v>
       </c>
       <c r="I27" t="n">
-        <v>839</v>
+        <v>772</v>
       </c>
       <c r="J27" t="n">
-        <v>691</v>
+        <v>747</v>
       </c>
       <c r="K27" t="n">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="L27" t="n">
-        <v>749</v>
+        <v>737.5</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>675</v>
+        <v>642</v>
       </c>
       <c r="C28" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D28" t="n">
-        <v>624</v>
+        <v>672</v>
       </c>
       <c r="E28" t="n">
-        <v>612</v>
+        <v>667</v>
       </c>
       <c r="F28" t="n">
-        <v>652</v>
+        <v>590</v>
       </c>
       <c r="G28" t="n">
-        <v>745</v>
+        <v>725</v>
       </c>
       <c r="H28" t="n">
-        <v>695</v>
+        <v>641</v>
       </c>
       <c r="I28" t="n">
-        <v>629</v>
+        <v>824</v>
       </c>
       <c r="J28" t="n">
-        <v>668</v>
+        <v>693</v>
       </c>
       <c r="K28" t="n">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="L28" t="n">
-        <v>656</v>
+        <v>671.5</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>664</v>
+        <v>748</v>
       </c>
       <c r="C29" t="n">
-        <v>738</v>
+        <v>651</v>
       </c>
       <c r="D29" t="n">
-        <v>643</v>
+        <v>658</v>
       </c>
       <c r="E29" t="n">
-        <v>589</v>
+        <v>670</v>
       </c>
       <c r="F29" t="n">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="G29" t="n">
-        <v>694</v>
+        <v>742</v>
       </c>
       <c r="H29" t="n">
-        <v>704</v>
+        <v>783</v>
       </c>
       <c r="I29" t="n">
-        <v>670</v>
+        <v>652</v>
       </c>
       <c r="J29" t="n">
-        <v>805</v>
+        <v>623</v>
       </c>
       <c r="K29" t="n">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="L29" t="n">
-        <v>692.8</v>
+        <v>693.9</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>595</v>
+        <v>755</v>
       </c>
       <c r="C30" t="n">
-        <v>694</v>
+        <v>632</v>
       </c>
       <c r="D30" t="n">
-        <v>714</v>
+        <v>639</v>
       </c>
       <c r="E30" t="n">
-        <v>688</v>
+        <v>733</v>
       </c>
       <c r="F30" t="n">
-        <v>657</v>
+        <v>605</v>
       </c>
       <c r="G30" t="n">
-        <v>694</v>
+        <v>653</v>
       </c>
       <c r="H30" t="n">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="I30" t="n">
-        <v>811</v>
+        <v>695</v>
       </c>
       <c r="J30" t="n">
-        <v>744</v>
+        <v>766</v>
       </c>
       <c r="K30" t="n">
-        <v>782</v>
+        <v>767</v>
       </c>
       <c r="L30" t="n">
-        <v>706</v>
+        <v>693.5</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>808</v>
+        <v>671</v>
       </c>
       <c r="C31" t="n">
-        <v>699</v>
+        <v>673</v>
       </c>
       <c r="D31" t="n">
-        <v>681</v>
+        <v>783</v>
       </c>
       <c r="E31" t="n">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="F31" t="n">
-        <v>831</v>
+        <v>665</v>
       </c>
       <c r="G31" t="n">
-        <v>641</v>
+        <v>737</v>
       </c>
       <c r="H31" t="n">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="I31" t="n">
-        <v>791</v>
+        <v>708</v>
       </c>
       <c r="J31" t="n">
-        <v>738</v>
+        <v>698</v>
       </c>
       <c r="K31" t="n">
-        <v>688</v>
+        <v>826</v>
       </c>
       <c r="L31" t="n">
-        <v>726.3</v>
+        <v>713.7</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>602</v>
+        <v>541</v>
       </c>
       <c r="C32" t="n">
-        <v>617</v>
+        <v>640</v>
       </c>
       <c r="D32" t="n">
-        <v>707</v>
+        <v>572</v>
       </c>
       <c r="E32" t="n">
-        <v>727</v>
+        <v>608</v>
       </c>
       <c r="F32" t="n">
-        <v>529</v>
+        <v>647</v>
       </c>
       <c r="G32" t="n">
-        <v>710</v>
+        <v>584</v>
       </c>
       <c r="H32" t="n">
-        <v>633</v>
+        <v>656</v>
       </c>
       <c r="I32" t="n">
-        <v>657</v>
+        <v>590</v>
       </c>
       <c r="J32" t="n">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="K32" t="n">
-        <v>639</v>
+        <v>612</v>
       </c>
       <c r="L32" t="n">
-        <v>643.7</v>
+        <v>605</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>826</v>
+        <v>760</v>
       </c>
       <c r="C33" t="n">
+        <v>735</v>
+      </c>
+      <c r="D33" t="n">
+        <v>816</v>
+      </c>
+      <c r="E33" t="n">
+        <v>698</v>
+      </c>
+      <c r="F33" t="n">
+        <v>802</v>
+      </c>
+      <c r="G33" t="n">
+        <v>716</v>
+      </c>
+      <c r="H33" t="n">
         <v>720</v>
       </c>
-      <c r="D33" t="n">
-        <v>718</v>
-      </c>
-      <c r="E33" t="n">
-        <v>706</v>
-      </c>
-      <c r="F33" t="n">
-        <v>702</v>
-      </c>
-      <c r="G33" t="n">
-        <v>750</v>
-      </c>
-      <c r="H33" t="n">
-        <v>701</v>
-      </c>
       <c r="I33" t="n">
-        <v>826</v>
+        <v>681</v>
       </c>
       <c r="J33" t="n">
-        <v>786</v>
+        <v>764</v>
       </c>
       <c r="K33" t="n">
-        <v>760</v>
+        <v>719</v>
       </c>
       <c r="L33" t="n">
-        <v>749.5</v>
+        <v>741.1</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>633</v>
+        <v>694</v>
       </c>
       <c r="C34" t="n">
-        <v>577</v>
+        <v>665</v>
       </c>
       <c r="D34" t="n">
-        <v>670</v>
+        <v>703</v>
       </c>
       <c r="E34" t="n">
-        <v>729</v>
+        <v>696</v>
       </c>
       <c r="F34" t="n">
-        <v>657</v>
+        <v>579</v>
       </c>
       <c r="G34" t="n">
-        <v>681</v>
+        <v>592</v>
       </c>
       <c r="H34" t="n">
-        <v>592</v>
+        <v>680</v>
       </c>
       <c r="I34" t="n">
-        <v>593</v>
+        <v>625</v>
       </c>
       <c r="J34" t="n">
-        <v>636</v>
+        <v>565</v>
       </c>
       <c r="K34" t="n">
-        <v>685</v>
+        <v>658</v>
       </c>
       <c r="L34" t="n">
-        <v>645.3</v>
+        <v>645.7</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="C35" t="n">
-        <v>748</v>
+        <v>781</v>
       </c>
       <c r="D35" t="n">
-        <v>764</v>
+        <v>884</v>
       </c>
       <c r="E35" t="n">
-        <v>816</v>
+        <v>674</v>
       </c>
       <c r="F35" t="n">
-        <v>735</v>
+        <v>809</v>
       </c>
       <c r="G35" t="n">
-        <v>808</v>
+        <v>738</v>
       </c>
       <c r="H35" t="n">
-        <v>789</v>
+        <v>754</v>
       </c>
       <c r="I35" t="n">
-        <v>701</v>
+        <v>780</v>
       </c>
       <c r="J35" t="n">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="K35" t="n">
-        <v>705</v>
+        <v>881</v>
       </c>
       <c r="L35" t="n">
-        <v>758.9</v>
+        <v>783.5</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="C36" t="n">
-        <v>595</v>
+        <v>678</v>
       </c>
       <c r="D36" t="n">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="E36" t="n">
-        <v>680</v>
+        <v>618</v>
       </c>
       <c r="F36" t="n">
+        <v>623</v>
+      </c>
+      <c r="G36" t="n">
+        <v>634</v>
+      </c>
+      <c r="H36" t="n">
         <v>598</v>
       </c>
-      <c r="G36" t="n">
-        <v>620</v>
-      </c>
-      <c r="H36" t="n">
-        <v>553</v>
-      </c>
       <c r="I36" t="n">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="J36" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K36" t="n">
-        <v>657</v>
+        <v>583</v>
       </c>
       <c r="L36" t="n">
-        <v>616.4</v>
+        <v>618.7</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>646</v>
+        <v>758</v>
       </c>
       <c r="C37" t="n">
-        <v>808</v>
+        <v>768</v>
       </c>
       <c r="D37" t="n">
-        <v>729</v>
+        <v>785</v>
       </c>
       <c r="E37" t="n">
-        <v>664</v>
+        <v>633</v>
       </c>
       <c r="F37" t="n">
-        <v>643</v>
+        <v>803</v>
       </c>
       <c r="G37" t="n">
-        <v>702</v>
+        <v>790</v>
       </c>
       <c r="H37" t="n">
-        <v>685</v>
+        <v>762</v>
       </c>
       <c r="I37" t="n">
-        <v>756</v>
+        <v>774</v>
       </c>
       <c r="J37" t="n">
-        <v>726</v>
+        <v>742</v>
       </c>
       <c r="K37" t="n">
-        <v>705</v>
+        <v>762</v>
       </c>
       <c r="L37" t="n">
-        <v>706.4</v>
+        <v>757.7</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>745</v>
+        <v>693</v>
       </c>
       <c r="C38" t="n">
-        <v>748</v>
+        <v>699</v>
       </c>
       <c r="D38" t="n">
-        <v>676</v>
+        <v>697</v>
       </c>
       <c r="E38" t="n">
-        <v>728</v>
+        <v>700</v>
       </c>
       <c r="F38" t="n">
+        <v>677</v>
+      </c>
+      <c r="G38" t="n">
+        <v>746</v>
+      </c>
+      <c r="H38" t="n">
+        <v>704</v>
+      </c>
+      <c r="I38" t="n">
         <v>694</v>
       </c>
-      <c r="G38" t="n">
-        <v>808</v>
-      </c>
-      <c r="H38" t="n">
-        <v>708</v>
-      </c>
-      <c r="I38" t="n">
-        <v>788</v>
-      </c>
       <c r="J38" t="n">
-        <v>898</v>
+        <v>719</v>
       </c>
       <c r="K38" t="n">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="L38" t="n">
-        <v>756.2</v>
+        <v>709</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>631</v>
+        <v>580</v>
       </c>
       <c r="C39" t="n">
+        <v>585</v>
+      </c>
+      <c r="D39" t="n">
+        <v>612</v>
+      </c>
+      <c r="E39" t="n">
+        <v>615</v>
+      </c>
+      <c r="F39" t="n">
+        <v>612</v>
+      </c>
+      <c r="G39" t="n">
+        <v>607</v>
+      </c>
+      <c r="H39" t="n">
         <v>588</v>
       </c>
-      <c r="D39" t="n">
-        <v>584</v>
-      </c>
-      <c r="E39" t="n">
-        <v>627</v>
-      </c>
-      <c r="F39" t="n">
-        <v>531</v>
-      </c>
-      <c r="G39" t="n">
-        <v>554</v>
-      </c>
-      <c r="H39" t="n">
-        <v>676</v>
-      </c>
       <c r="I39" t="n">
-        <v>629</v>
+        <v>582</v>
       </c>
       <c r="J39" t="n">
-        <v>651</v>
+        <v>527</v>
       </c>
       <c r="K39" t="n">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="L39" t="n">
-        <v>606.1</v>
+        <v>590.5</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>702</v>
+        <v>739</v>
       </c>
       <c r="C40" t="n">
-        <v>691</v>
+        <v>732</v>
       </c>
       <c r="D40" t="n">
-        <v>685</v>
+        <v>781</v>
       </c>
       <c r="E40" t="n">
-        <v>693</v>
+        <v>664</v>
       </c>
       <c r="F40" t="n">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="G40" t="n">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="H40" t="n">
-        <v>795</v>
+        <v>732</v>
       </c>
       <c r="I40" t="n">
-        <v>743</v>
+        <v>717</v>
       </c>
       <c r="J40" t="n">
-        <v>748</v>
+        <v>785</v>
       </c>
       <c r="K40" t="n">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="L40" t="n">
-        <v>728.9</v>
+        <v>739</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>675</v>
+        <v>733</v>
       </c>
       <c r="C41" t="n">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="D41" t="n">
-        <v>662</v>
+        <v>638</v>
       </c>
       <c r="E41" t="n">
-        <v>613</v>
+        <v>719</v>
       </c>
       <c r="F41" t="n">
-        <v>705</v>
+        <v>753</v>
       </c>
       <c r="G41" t="n">
-        <v>631</v>
+        <v>682</v>
       </c>
       <c r="H41" t="n">
-        <v>698</v>
+        <v>758</v>
       </c>
       <c r="I41" t="n">
-        <v>698</v>
+        <v>616</v>
       </c>
       <c r="J41" t="n">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="K41" t="n">
-        <v>723</v>
+        <v>636</v>
       </c>
       <c r="L41" t="n">
-        <v>679.6</v>
+        <v>692.9</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>713</v>
+        <v>542</v>
       </c>
       <c r="C42" t="n">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="D42" t="n">
-        <v>605</v>
+        <v>531</v>
       </c>
       <c r="E42" t="n">
-        <v>631</v>
+        <v>663</v>
       </c>
       <c r="F42" t="n">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="G42" t="n">
-        <v>584</v>
+        <v>627</v>
       </c>
       <c r="H42" t="n">
-        <v>549</v>
+        <v>598</v>
       </c>
       <c r="I42" t="n">
-        <v>590</v>
+        <v>661</v>
       </c>
       <c r="J42" t="n">
-        <v>631</v>
+        <v>535</v>
       </c>
       <c r="K42" t="n">
-        <v>703</v>
+        <v>614</v>
       </c>
       <c r="L42" t="n">
-        <v>626.8</v>
+        <v>603.4</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>598</v>
+        <v>635</v>
       </c>
       <c r="C43" t="n">
+        <v>669</v>
+      </c>
+      <c r="D43" t="n">
+        <v>708</v>
+      </c>
+      <c r="E43" t="n">
+        <v>636</v>
+      </c>
+      <c r="F43" t="n">
+        <v>702</v>
+      </c>
+      <c r="G43" t="n">
+        <v>685</v>
+      </c>
+      <c r="H43" t="n">
         <v>653</v>
       </c>
-      <c r="D43" t="n">
-        <v>671</v>
-      </c>
-      <c r="E43" t="n">
-        <v>617</v>
-      </c>
-      <c r="F43" t="n">
-        <v>663</v>
-      </c>
-      <c r="G43" t="n">
-        <v>632</v>
-      </c>
-      <c r="H43" t="n">
-        <v>663</v>
-      </c>
       <c r="I43" t="n">
-        <v>750</v>
+        <v>687</v>
       </c>
       <c r="J43" t="n">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="K43" t="n">
-        <v>633</v>
+        <v>725</v>
       </c>
       <c r="L43" t="n">
-        <v>658.1</v>
+        <v>678.8</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>657</v>
+        <v>712</v>
       </c>
       <c r="C44" t="n">
-        <v>857</v>
+        <v>784</v>
       </c>
       <c r="D44" t="n">
-        <v>713</v>
+        <v>840</v>
       </c>
       <c r="E44" t="n">
-        <v>786</v>
+        <v>687</v>
       </c>
       <c r="F44" t="n">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="G44" t="n">
-        <v>732</v>
+        <v>782</v>
       </c>
       <c r="H44" t="n">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="I44" t="n">
-        <v>728</v>
+        <v>870</v>
       </c>
       <c r="J44" t="n">
-        <v>788</v>
+        <v>716</v>
       </c>
       <c r="K44" t="n">
-        <v>733</v>
+        <v>790</v>
       </c>
       <c r="L44" t="n">
-        <v>748.2</v>
+        <v>766.5</v>
       </c>
     </row>
     <row r="45">
@@ -2108,34 +2108,34 @@
         <v>622</v>
       </c>
       <c r="C45" t="n">
-        <v>598</v>
+        <v>649</v>
       </c>
       <c r="D45" t="n">
-        <v>608</v>
+        <v>541</v>
       </c>
       <c r="E45" t="n">
-        <v>550</v>
+        <v>639</v>
       </c>
       <c r="F45" t="n">
+        <v>572</v>
+      </c>
+      <c r="G45" t="n">
+        <v>686</v>
+      </c>
+      <c r="H45" t="n">
         <v>564</v>
       </c>
-      <c r="G45" t="n">
-        <v>579</v>
-      </c>
-      <c r="H45" t="n">
-        <v>609</v>
-      </c>
       <c r="I45" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
       <c r="J45" t="n">
-        <v>638</v>
+        <v>588</v>
       </c>
       <c r="K45" t="n">
-        <v>681</v>
+        <v>553</v>
       </c>
       <c r="L45" t="n">
-        <v>607.5</v>
+        <v>596.2</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>667</v>
+        <v>698</v>
       </c>
       <c r="C46" t="n">
-        <v>662</v>
+        <v>599</v>
       </c>
       <c r="D46" t="n">
-        <v>675</v>
+        <v>652</v>
       </c>
       <c r="E46" t="n">
-        <v>626</v>
+        <v>783</v>
       </c>
       <c r="F46" t="n">
-        <v>642</v>
+        <v>722</v>
       </c>
       <c r="G46" t="n">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="H46" t="n">
-        <v>586</v>
+        <v>687</v>
       </c>
       <c r="I46" t="n">
-        <v>679</v>
+        <v>722</v>
       </c>
       <c r="J46" t="n">
-        <v>699</v>
+        <v>780</v>
       </c>
       <c r="K46" t="n">
-        <v>683</v>
+        <v>600</v>
       </c>
       <c r="L46" t="n">
-        <v>658.5</v>
+        <v>688.6</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>812</v>
+        <v>786</v>
       </c>
       <c r="C47" t="n">
-        <v>843</v>
+        <v>747</v>
       </c>
       <c r="D47" t="n">
-        <v>758</v>
+        <v>707</v>
       </c>
       <c r="E47" t="n">
-        <v>915</v>
+        <v>788</v>
       </c>
       <c r="F47" t="n">
-        <v>739</v>
+        <v>690</v>
       </c>
       <c r="G47" t="n">
-        <v>722</v>
+        <v>658</v>
       </c>
       <c r="H47" t="n">
-        <v>693</v>
+        <v>756</v>
       </c>
       <c r="I47" t="n">
-        <v>627</v>
+        <v>813</v>
       </c>
       <c r="J47" t="n">
-        <v>715</v>
+        <v>860</v>
       </c>
       <c r="K47" t="n">
-        <v>657</v>
+        <v>714</v>
       </c>
       <c r="L47" t="n">
-        <v>748.1</v>
+        <v>751.9</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>687</v>
+        <v>613</v>
       </c>
       <c r="C48" t="n">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D48" t="n">
-        <v>756</v>
+        <v>648</v>
       </c>
       <c r="E48" t="n">
-        <v>623</v>
+        <v>647</v>
       </c>
       <c r="F48" t="n">
-        <v>664</v>
+        <v>626</v>
       </c>
       <c r="G48" t="n">
-        <v>662</v>
+        <v>626</v>
       </c>
       <c r="H48" t="n">
-        <v>593</v>
+        <v>765</v>
       </c>
       <c r="I48" t="n">
-        <v>648</v>
+        <v>679</v>
       </c>
       <c r="J48" t="n">
-        <v>738</v>
+        <v>655</v>
       </c>
       <c r="K48" t="n">
-        <v>720</v>
+        <v>619</v>
       </c>
       <c r="L48" t="n">
-        <v>675.7</v>
+        <v>654.3</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>768</v>
+        <v>831</v>
       </c>
       <c r="C49" t="n">
+        <v>769</v>
+      </c>
+      <c r="D49" t="n">
+        <v>749</v>
+      </c>
+      <c r="E49" t="n">
+        <v>745</v>
+      </c>
+      <c r="F49" t="n">
+        <v>741</v>
+      </c>
+      <c r="G49" t="n">
+        <v>851</v>
+      </c>
+      <c r="H49" t="n">
+        <v>735</v>
+      </c>
+      <c r="I49" t="n">
+        <v>822</v>
+      </c>
+      <c r="J49" t="n">
         <v>724</v>
       </c>
-      <c r="D49" t="n">
-        <v>771</v>
-      </c>
-      <c r="E49" t="n">
-        <v>841</v>
-      </c>
-      <c r="F49" t="n">
-        <v>829</v>
-      </c>
-      <c r="G49" t="n">
-        <v>845</v>
-      </c>
-      <c r="H49" t="n">
-        <v>753</v>
-      </c>
-      <c r="I49" t="n">
-        <v>731</v>
-      </c>
-      <c r="J49" t="n">
-        <v>800</v>
-      </c>
       <c r="K49" t="n">
-        <v>697</v>
+        <v>880</v>
       </c>
       <c r="L49" t="n">
-        <v>775.9</v>
+        <v>784.7</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>706</v>
+        <v>669</v>
       </c>
       <c r="C50" t="n">
-        <v>682</v>
+        <v>644</v>
       </c>
       <c r="D50" t="n">
-        <v>561</v>
+        <v>679</v>
       </c>
       <c r="E50" t="n">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="F50" t="n">
-        <v>584</v>
+        <v>623</v>
       </c>
       <c r="G50" t="n">
-        <v>693</v>
+        <v>571</v>
       </c>
       <c r="H50" t="n">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="I50" t="n">
-        <v>606</v>
+        <v>632</v>
       </c>
       <c r="J50" t="n">
-        <v>641</v>
+        <v>607</v>
       </c>
       <c r="K50" t="n">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="L50" t="n">
-        <v>652.8</v>
+        <v>647.4</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>695</v>
+        <v>657</v>
       </c>
       <c r="C51" t="n">
-        <v>634</v>
+        <v>762</v>
       </c>
       <c r="D51" t="n">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E51" t="n">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="F51" t="n">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="G51" t="n">
-        <v>721</v>
+        <v>656</v>
       </c>
       <c r="H51" t="n">
-        <v>696</v>
+        <v>652</v>
       </c>
       <c r="I51" t="n">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="J51" t="n">
-        <v>638</v>
+        <v>690</v>
       </c>
       <c r="K51" t="n">
-        <v>650</v>
+        <v>725</v>
       </c>
       <c r="L51" t="n">
-        <v>673.1</v>
+        <v>683.5</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>703.7</v>
+        <v>690.6</v>
       </c>
       <c r="C52" t="n">
-        <v>695.42</v>
+        <v>684.54</v>
       </c>
       <c r="D52" t="n">
-        <v>683.58</v>
+        <v>686.8</v>
       </c>
       <c r="E52" t="n">
-        <v>691.8200000000001</v>
+        <v>691.36</v>
       </c>
       <c r="F52" t="n">
-        <v>691.92</v>
+        <v>695.0599999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>692.3200000000001</v>
+        <v>697.52</v>
       </c>
       <c r="H52" t="n">
-        <v>683.86</v>
+        <v>687.24</v>
       </c>
       <c r="I52" t="n">
-        <v>700.16</v>
+        <v>697.74</v>
       </c>
       <c r="J52" t="n">
-        <v>702.26</v>
+        <v>692.08</v>
       </c>
       <c r="K52" t="n">
-        <v>692.72</v>
+        <v>693.2</v>
       </c>
       <c r="L52" t="n">
-        <v>693.7760000000001</v>
+        <v>691.614</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.20933723449707</v>
+        <v>4.402791023254395</v>
       </c>
       <c r="C2" t="n">
-        <v>4.037635326385498</v>
+        <v>4.383856773376465</v>
       </c>
       <c r="D2" t="n">
-        <v>4.222417831420898</v>
+        <v>3.952451229095459</v>
       </c>
       <c r="E2" t="n">
-        <v>4.489411115646362</v>
+        <v>4.023988246917725</v>
       </c>
       <c r="F2" t="n">
-        <v>4.067833185195923</v>
+        <v>4.44792366027832</v>
       </c>
       <c r="G2" t="n">
-        <v>4.161692380905151</v>
+        <v>4.037478685379028</v>
       </c>
       <c r="H2" t="n">
-        <v>4.154096126556396</v>
+        <v>4.480848073959351</v>
       </c>
       <c r="I2" t="n">
-        <v>4.037053108215332</v>
+        <v>4.179627895355225</v>
       </c>
       <c r="J2" t="n">
-        <v>4.200006484985352</v>
+        <v>4.156175851821899</v>
       </c>
       <c r="K2" t="n">
-        <v>4.094150304794312</v>
+        <v>4.004593372344971</v>
       </c>
       <c r="L2" t="n">
-        <v>4.16736330986023</v>
+        <v>4.206973481178284</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.444227457046509</v>
+        <v>4.400527000427246</v>
       </c>
       <c r="C3" t="n">
-        <v>4.188316822052002</v>
+        <v>4.846386194229126</v>
       </c>
       <c r="D3" t="n">
-        <v>5.650135040283203</v>
+        <v>4.513741016387939</v>
       </c>
       <c r="E3" t="n">
-        <v>4.847703218460083</v>
+        <v>4.930161237716675</v>
       </c>
       <c r="F3" t="n">
-        <v>5.084722757339478</v>
+        <v>4.781043529510498</v>
       </c>
       <c r="G3" t="n">
-        <v>4.885487794876099</v>
+        <v>5.347087144851685</v>
       </c>
       <c r="H3" t="n">
-        <v>4.732654333114624</v>
+        <v>4.306280374526978</v>
       </c>
       <c r="I3" t="n">
-        <v>4.647617340087891</v>
+        <v>4.503761291503906</v>
       </c>
       <c r="J3" t="n">
-        <v>4.366770029067993</v>
+        <v>4.492312669754028</v>
       </c>
       <c r="K3" t="n">
-        <v>4.885639905929565</v>
+        <v>4.279356718063354</v>
       </c>
       <c r="L3" t="n">
-        <v>4.773327469825745</v>
+        <v>4.640065717697143</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>4.586908340454102</v>
+        <v>4.528753042221069</v>
       </c>
       <c r="C4" t="n">
-        <v>4.817739009857178</v>
+        <v>4.398533821105957</v>
       </c>
       <c r="D4" t="n">
-        <v>4.378998994827271</v>
+        <v>4.660375595092773</v>
       </c>
       <c r="E4" t="n">
-        <v>4.420217990875244</v>
+        <v>4.453387498855591</v>
       </c>
       <c r="F4" t="n">
-        <v>5.341526985168457</v>
+        <v>4.536687135696411</v>
       </c>
       <c r="G4" t="n">
-        <v>4.661505460739136</v>
+        <v>4.484827518463135</v>
       </c>
       <c r="H4" t="n">
-        <v>4.479205369949341</v>
+        <v>4.89673113822937</v>
       </c>
       <c r="I4" t="n">
-        <v>4.611445903778076</v>
+        <v>4.275382280349731</v>
       </c>
       <c r="J4" t="n">
-        <v>5.006714344024658</v>
+        <v>4.716525793075562</v>
       </c>
       <c r="K4" t="n">
-        <v>4.638488531112671</v>
+        <v>4.567845821380615</v>
       </c>
       <c r="L4" t="n">
-        <v>4.694275093078613</v>
+        <v>4.551904964447021</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>5.063264846801758</v>
+        <v>5.182804346084595</v>
       </c>
       <c r="C5" t="n">
-        <v>5.093783378601074</v>
+        <v>5.334899187088013</v>
       </c>
       <c r="D5" t="n">
-        <v>4.985952377319336</v>
+        <v>5.048615694046021</v>
       </c>
       <c r="E5" t="n">
-        <v>5.044443845748901</v>
+        <v>5.204717397689819</v>
       </c>
       <c r="F5" t="n">
-        <v>5.115296363830566</v>
+        <v>4.876431703567505</v>
       </c>
       <c r="G5" t="n">
-        <v>5.222004652023315</v>
+        <v>5.482217073440552</v>
       </c>
       <c r="H5" t="n">
-        <v>5.399075031280518</v>
+        <v>5.604263544082642</v>
       </c>
       <c r="I5" t="n">
-        <v>5.122146844863892</v>
+        <v>4.977038145065308</v>
       </c>
       <c r="J5" t="n">
-        <v>5.062427043914795</v>
+        <v>4.783024549484253</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2914879322052</v>
+        <v>4.961082696914673</v>
       </c>
       <c r="L5" t="n">
-        <v>5.139988231658935</v>
+        <v>5.145509433746338</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>3.769274950027466</v>
+        <v>3.98762845993042</v>
       </c>
       <c r="C6" t="n">
-        <v>3.932106494903564</v>
+        <v>3.9183189868927</v>
       </c>
       <c r="D6" t="n">
-        <v>3.826887845993042</v>
+        <v>3.728796720504761</v>
       </c>
       <c r="E6" t="n">
-        <v>3.853670597076416</v>
+        <v>3.942234039306641</v>
       </c>
       <c r="F6" t="n">
-        <v>4.221500158309937</v>
+        <v>3.758212566375732</v>
       </c>
       <c r="G6" t="n">
-        <v>4.041005373001099</v>
+        <v>4.251928567886353</v>
       </c>
       <c r="H6" t="n">
-        <v>3.819698095321655</v>
+        <v>3.945721626281738</v>
       </c>
       <c r="I6" t="n">
-        <v>4.181178569793701</v>
+        <v>3.995650053024292</v>
       </c>
       <c r="J6" t="n">
-        <v>4.151692628860474</v>
+        <v>4.340195894241333</v>
       </c>
       <c r="K6" t="n">
-        <v>4.22200870513916</v>
+        <v>3.910322666168213</v>
       </c>
       <c r="L6" t="n">
-        <v>4.001902341842651</v>
+        <v>3.977900958061218</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>4.886819839477539</v>
+        <v>4.577576875686646</v>
       </c>
       <c r="C7" t="n">
-        <v>4.895638942718506</v>
+        <v>4.876460075378418</v>
       </c>
       <c r="D7" t="n">
-        <v>4.909772157669067</v>
+        <v>4.985269784927368</v>
       </c>
       <c r="E7" t="n">
-        <v>5.056426286697388</v>
+        <v>5.202736377716064</v>
       </c>
       <c r="F7" t="n">
-        <v>4.950542688369751</v>
+        <v>4.957873344421387</v>
       </c>
       <c r="G7" t="n">
-        <v>4.727695226669312</v>
+        <v>4.681553840637207</v>
       </c>
       <c r="H7" t="n">
-        <v>4.709835290908813</v>
+        <v>5.206726789474487</v>
       </c>
       <c r="I7" t="n">
-        <v>4.796596527099609</v>
+        <v>4.801754951477051</v>
       </c>
       <c r="J7" t="n">
-        <v>4.754454135894775</v>
+        <v>4.479571342468262</v>
       </c>
       <c r="K7" t="n">
-        <v>4.63884162902832</v>
+        <v>4.980319976806641</v>
       </c>
       <c r="L7" t="n">
-        <v>4.832662272453308</v>
+        <v>4.874984335899353</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>4.156652688980103</v>
+        <v>3.940950870513916</v>
       </c>
       <c r="C8" t="n">
-        <v>3.984194755554199</v>
+        <v>3.993317365646362</v>
       </c>
       <c r="D8" t="n">
-        <v>4.290584325790405</v>
+        <v>4.038202047348022</v>
       </c>
       <c r="E8" t="n">
-        <v>4.399192094802856</v>
+        <v>4.298546314239502</v>
       </c>
       <c r="F8" t="n">
-        <v>4.57248592376709</v>
+        <v>4.429699897766113</v>
       </c>
       <c r="G8" t="n">
-        <v>4.06403112411499</v>
+        <v>4.043691635131836</v>
       </c>
       <c r="H8" t="n">
-        <v>4.18398642539978</v>
+        <v>3.953941583633423</v>
       </c>
       <c r="I8" t="n">
-        <v>4.198845386505127</v>
+        <v>4.147928953170776</v>
       </c>
       <c r="J8" t="n">
-        <v>4.182473659515381</v>
+        <v>4.396814584732056</v>
       </c>
       <c r="K8" t="n">
-        <v>4.086923122406006</v>
+        <v>3.971374988555908</v>
       </c>
       <c r="L8" t="n">
-        <v>4.211936950683594</v>
+        <v>4.121446824073791</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.668839693069458</v>
+        <v>3.984330177307129</v>
       </c>
       <c r="C9" t="n">
-        <v>3.903115272521973</v>
+        <v>4.042185306549072</v>
       </c>
       <c r="D9" t="n">
-        <v>4.070896148681641</v>
+        <v>3.850177764892578</v>
       </c>
       <c r="E9" t="n">
-        <v>3.728336811065674</v>
+        <v>3.914571762084961</v>
       </c>
       <c r="F9" t="n">
-        <v>3.942711353302002</v>
+        <v>3.938537836074829</v>
       </c>
       <c r="G9" t="n">
-        <v>3.819629430770874</v>
+        <v>4.045216798782349</v>
       </c>
       <c r="H9" t="n">
-        <v>3.876003980636597</v>
+        <v>3.706045150756836</v>
       </c>
       <c r="I9" t="n">
-        <v>4.341778039932251</v>
+        <v>4.175829887390137</v>
       </c>
       <c r="J9" t="n">
-        <v>4.261476516723633</v>
+        <v>4.275604486465454</v>
       </c>
       <c r="K9" t="n">
-        <v>3.861711978912354</v>
+        <v>4.288569450378418</v>
       </c>
       <c r="L9" t="n">
-        <v>3.947449922561646</v>
+        <v>4.022106862068176</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>5.352894067764282</v>
+        <v>4.956377267837524</v>
       </c>
       <c r="C10" t="n">
-        <v>5.020791530609131</v>
+        <v>4.657122611999512</v>
       </c>
       <c r="D10" t="n">
-        <v>5.022780895233154</v>
+        <v>5.066602945327759</v>
       </c>
       <c r="E10" t="n">
-        <v>5.563391208648682</v>
+        <v>4.794284820556641</v>
       </c>
       <c r="F10" t="n">
-        <v>5.271160840988159</v>
+        <v>5.113500833511353</v>
       </c>
       <c r="G10" t="n">
-        <v>5.103005170822144</v>
+        <v>4.772825002670288</v>
       </c>
       <c r="H10" t="n">
-        <v>4.917110919952393</v>
+        <v>4.799505472183228</v>
       </c>
       <c r="I10" t="n">
-        <v>4.920593500137329</v>
+        <v>5.044875860214233</v>
       </c>
       <c r="J10" t="n">
-        <v>4.678161144256592</v>
+        <v>4.899754762649536</v>
       </c>
       <c r="K10" t="n">
-        <v>5.18243408203125</v>
+        <v>4.717227697372437</v>
       </c>
       <c r="L10" t="n">
-        <v>5.103232336044312</v>
+        <v>4.882207727432251</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.60347580909729</v>
+        <v>4.156183958053589</v>
       </c>
       <c r="C11" t="n">
-        <v>5.66011643409729</v>
+        <v>4.295320272445679</v>
       </c>
       <c r="D11" t="n">
-        <v>4.962801933288574</v>
+        <v>4.442421674728394</v>
       </c>
       <c r="E11" t="n">
-        <v>5.158881425857544</v>
+        <v>4.630938529968262</v>
       </c>
       <c r="F11" t="n">
-        <v>4.380810499191284</v>
+        <v>4.29530930519104</v>
       </c>
       <c r="G11" t="n">
-        <v>4.463748216629028</v>
+        <v>4.397565603256226</v>
       </c>
       <c r="H11" t="n">
-        <v>4.263745307922363</v>
+        <v>4.366615772247314</v>
       </c>
       <c r="I11" t="n">
-        <v>4.50480580329895</v>
+        <v>4.379091024398804</v>
       </c>
       <c r="J11" t="n">
-        <v>4.642520904541016</v>
+        <v>4.268397808074951</v>
       </c>
       <c r="K11" t="n">
-        <v>4.650716066360474</v>
+        <v>4.436427116394043</v>
       </c>
       <c r="L11" t="n">
-        <v>4.729162240028382</v>
+        <v>4.36682710647583</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>4.225798606872559</v>
+        <v>3.844994068145752</v>
       </c>
       <c r="C12" t="n">
-        <v>4.051832437515259</v>
+        <v>4.064910650253296</v>
       </c>
       <c r="D12" t="n">
-        <v>4.068302869796753</v>
+        <v>4.160175800323486</v>
       </c>
       <c r="E12" t="n">
-        <v>4.07186222076416</v>
+        <v>3.949301958084106</v>
       </c>
       <c r="F12" t="n">
-        <v>4.044101476669312</v>
+        <v>3.990640878677368</v>
       </c>
       <c r="G12" t="n">
-        <v>4.111737489700317</v>
+        <v>4.083867073059082</v>
       </c>
       <c r="H12" t="n">
-        <v>4.078280687332153</v>
+        <v>4.037501096725464</v>
       </c>
       <c r="I12" t="n">
-        <v>4.000707864761353</v>
+        <v>3.970147132873535</v>
       </c>
       <c r="J12" t="n">
-        <v>3.973901987075806</v>
+        <v>3.982637882232666</v>
       </c>
       <c r="K12" t="n">
-        <v>4.079925298690796</v>
+        <v>4.215034961700439</v>
       </c>
       <c r="L12" t="n">
-        <v>4.070645093917847</v>
+        <v>4.029921150207519</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4.107642889022827</v>
+        <v>3.986605644226074</v>
       </c>
       <c r="C13" t="n">
-        <v>3.841971397399902</v>
+        <v>3.90831995010376</v>
       </c>
       <c r="D13" t="n">
-        <v>4.152607679367065</v>
+        <v>3.827023506164551</v>
       </c>
       <c r="E13" t="n">
-        <v>4.357442378997803</v>
+        <v>3.975646257400513</v>
       </c>
       <c r="F13" t="n">
-        <v>3.936253547668457</v>
+        <v>4.416073322296143</v>
       </c>
       <c r="G13" t="n">
-        <v>4.018239259719849</v>
+        <v>4.220012903213501</v>
       </c>
       <c r="H13" t="n">
-        <v>4.028494834899902</v>
+        <v>4.390594959259033</v>
       </c>
       <c r="I13" t="n">
-        <v>3.922305107116699</v>
+        <v>4.341032981872559</v>
       </c>
       <c r="J13" t="n">
-        <v>4.430221319198608</v>
+        <v>4.587342262268066</v>
       </c>
       <c r="K13" t="n">
-        <v>3.866246700286865</v>
+        <v>4.052176237106323</v>
       </c>
       <c r="L13" t="n">
-        <v>4.066142511367798</v>
+        <v>4.170482802391052</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.182453870773315</v>
+        <v>4.033707618713379</v>
       </c>
       <c r="C14" t="n">
-        <v>4.493356943130493</v>
+        <v>3.947429656982422</v>
       </c>
       <c r="D14" t="n">
-        <v>4.168723106384277</v>
+        <v>4.61229395866394</v>
       </c>
       <c r="E14" t="n">
-        <v>4.707180261611938</v>
+        <v>4.214282989501953</v>
       </c>
       <c r="F14" t="n">
-        <v>4.244495391845703</v>
+        <v>4.175387620925903</v>
       </c>
       <c r="G14" t="n">
-        <v>4.280653238296509</v>
+        <v>4.166373014450073</v>
       </c>
       <c r="H14" t="n">
-        <v>4.386932611465454</v>
+        <v>4.41473650932312</v>
       </c>
       <c r="I14" t="n">
-        <v>4.485782861709595</v>
+        <v>4.295544385910034</v>
       </c>
       <c r="J14" t="n">
-        <v>4.346843004226685</v>
+        <v>4.158881664276123</v>
       </c>
       <c r="K14" t="n">
-        <v>3.931543350219727</v>
+        <v>4.22820782661438</v>
       </c>
       <c r="L14" t="n">
-        <v>4.32279646396637</v>
+        <v>4.224684524536133</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>5.123047351837158</v>
+        <v>4.906044244766235</v>
       </c>
       <c r="C15" t="n">
-        <v>4.83460545539856</v>
+        <v>4.984279632568359</v>
       </c>
       <c r="D15" t="n">
-        <v>5.101396322250366</v>
+        <v>4.513010025024414</v>
       </c>
       <c r="E15" t="n">
-        <v>4.692062854766846</v>
+        <v>4.998245477676392</v>
       </c>
       <c r="F15" t="n">
-        <v>4.805927515029907</v>
+        <v>4.458614349365234</v>
       </c>
       <c r="G15" t="n">
-        <v>5.06934380531311</v>
+        <v>4.453145265579224</v>
       </c>
       <c r="H15" t="n">
-        <v>4.771661043167114</v>
+        <v>4.457627773284912</v>
       </c>
       <c r="I15" t="n">
-        <v>4.607725858688354</v>
+        <v>4.732955455780029</v>
       </c>
       <c r="J15" t="n">
-        <v>4.714287042617798</v>
+        <v>4.473236322402954</v>
       </c>
       <c r="K15" t="n">
-        <v>4.526238203048706</v>
+        <v>4.616251468658447</v>
       </c>
       <c r="L15" t="n">
-        <v>4.824629545211792</v>
+        <v>4.65934100151062</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.41969633102417</v>
+        <v>4.318497896194458</v>
       </c>
       <c r="C16" t="n">
-        <v>4.441453456878662</v>
+        <v>4.55642294883728</v>
       </c>
       <c r="D16" t="n">
-        <v>4.384446859359741</v>
+        <v>4.139943838119507</v>
       </c>
       <c r="E16" t="n">
-        <v>4.548938274383545</v>
+        <v>4.192317962646484</v>
       </c>
       <c r="F16" t="n">
-        <v>4.370982646942139</v>
+        <v>4.191322803497314</v>
       </c>
       <c r="G16" t="n">
-        <v>4.51227879524231</v>
+        <v>4.71747088432312</v>
       </c>
       <c r="H16" t="n">
-        <v>4.287692308425903</v>
+        <v>4.234194278717041</v>
       </c>
       <c r="I16" t="n">
-        <v>4.358654022216797</v>
+        <v>4.455157279968262</v>
       </c>
       <c r="J16" t="n">
-        <v>4.208125352859497</v>
+        <v>4.440675497055054</v>
       </c>
       <c r="K16" t="n">
-        <v>4.252617597579956</v>
+        <v>4.188324689865112</v>
       </c>
       <c r="L16" t="n">
-        <v>4.378488564491272</v>
+        <v>4.343432807922364</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.748886585235596</v>
+        <v>4.73442268371582</v>
       </c>
       <c r="C17" t="n">
-        <v>4.798977851867676</v>
+        <v>4.46811842918396</v>
       </c>
       <c r="D17" t="n">
-        <v>4.694838047027588</v>
+        <v>5.036153078079224</v>
       </c>
       <c r="E17" t="n">
-        <v>6.552433729171753</v>
+        <v>4.088093042373657</v>
       </c>
       <c r="F17" t="n">
-        <v>6.3889319896698</v>
+        <v>4.61926531791687</v>
       </c>
       <c r="G17" t="n">
-        <v>4.215099096298218</v>
+        <v>4.73642373085022</v>
       </c>
       <c r="H17" t="n">
-        <v>4.390050888061523</v>
+        <v>4.478111267089844</v>
       </c>
       <c r="I17" t="n">
-        <v>6.039902448654175</v>
+        <v>4.604270696640015</v>
       </c>
       <c r="J17" t="n">
-        <v>4.803067207336426</v>
+        <v>4.727437973022461</v>
       </c>
       <c r="K17" t="n">
-        <v>4.545282602310181</v>
+        <v>4.90299391746521</v>
       </c>
       <c r="L17" t="n">
-        <v>5.117747044563293</v>
+        <v>4.639529013633728</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>4.494095087051392</v>
+        <v>3.723995447158813</v>
       </c>
       <c r="C18" t="n">
-        <v>4.243752002716064</v>
+        <v>3.787338018417358</v>
       </c>
       <c r="D18" t="n">
-        <v>3.943007707595825</v>
+        <v>3.938452959060669</v>
       </c>
       <c r="E18" t="n">
-        <v>3.441834449768066</v>
+        <v>3.719097137451172</v>
       </c>
       <c r="F18" t="n">
-        <v>3.899991512298584</v>
+        <v>4.340698480606079</v>
       </c>
       <c r="G18" t="n">
-        <v>3.962319374084473</v>
+        <v>3.97116494178772</v>
       </c>
       <c r="H18" t="n">
-        <v>4.07654881477356</v>
+        <v>5.367194890975952</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7817223072052</v>
+        <v>4.148934125900269</v>
       </c>
       <c r="J18" t="n">
-        <v>3.882915496826172</v>
+        <v>3.912550926208496</v>
       </c>
       <c r="K18" t="n">
-        <v>3.787406206130981</v>
+        <v>4.108048915863037</v>
       </c>
       <c r="L18" t="n">
-        <v>3.951359295845032</v>
+        <v>4.101747584342957</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.616029500961304</v>
+        <v>4.66064190864563</v>
       </c>
       <c r="C19" t="n">
-        <v>4.489813804626465</v>
+        <v>4.257143259048462</v>
       </c>
       <c r="D19" t="n">
-        <v>4.193562984466553</v>
+        <v>4.526205062866211</v>
       </c>
       <c r="E19" t="n">
-        <v>4.196329355239868</v>
+        <v>4.588571548461914</v>
       </c>
       <c r="F19" t="n">
-        <v>4.555143594741821</v>
+        <v>4.718205690383911</v>
       </c>
       <c r="G19" t="n">
-        <v>4.314578056335449</v>
+        <v>4.741671562194824</v>
       </c>
       <c r="H19" t="n">
-        <v>4.393948554992676</v>
+        <v>4.370120286941528</v>
       </c>
       <c r="I19" t="n">
-        <v>4.26022481918335</v>
+        <v>4.461886167526245</v>
       </c>
       <c r="J19" t="n">
-        <v>4.065590381622314</v>
+        <v>4.810473203659058</v>
       </c>
       <c r="K19" t="n">
-        <v>4.436774253845215</v>
+        <v>4.718223094940186</v>
       </c>
       <c r="L19" t="n">
-        <v>4.352199530601501</v>
+        <v>4.585314178466797</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>4.306355953216553</v>
+        <v>4.130749225616455</v>
       </c>
       <c r="C20" t="n">
-        <v>4.104026794433594</v>
+        <v>4.319248199462891</v>
       </c>
       <c r="D20" t="n">
-        <v>4.095824718475342</v>
+        <v>4.8438880443573</v>
       </c>
       <c r="E20" t="n">
-        <v>4.436870574951172</v>
+        <v>4.65289306640625</v>
       </c>
       <c r="F20" t="n">
-        <v>4.030992031097412</v>
+        <v>4.426469802856445</v>
       </c>
       <c r="G20" t="n">
-        <v>4.43325400352478</v>
+        <v>4.403530359268188</v>
       </c>
       <c r="H20" t="n">
-        <v>4.019813537597656</v>
+        <v>4.650388240814209</v>
       </c>
       <c r="I20" t="n">
-        <v>4.035382509231567</v>
+        <v>4.298451662063599</v>
       </c>
       <c r="J20" t="n">
-        <v>4.440168857574463</v>
+        <v>4.214239358901978</v>
       </c>
       <c r="K20" t="n">
-        <v>4.086418628692627</v>
+        <v>4.242199420928955</v>
       </c>
       <c r="L20" t="n">
-        <v>4.198910760879516</v>
+        <v>4.418205738067627</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>4.589798450469971</v>
+        <v>4.334153652191162</v>
       </c>
       <c r="C21" t="n">
-        <v>4.604956150054932</v>
+        <v>4.323506593704224</v>
       </c>
       <c r="D21" t="n">
-        <v>4.389662027359009</v>
+        <v>4.458134651184082</v>
       </c>
       <c r="E21" t="n">
-        <v>4.130548715591431</v>
+        <v>5.024195194244385</v>
       </c>
       <c r="F21" t="n">
-        <v>4.419581651687622</v>
+        <v>4.273618221282959</v>
       </c>
       <c r="G21" t="n">
-        <v>4.072466135025024</v>
+        <v>4.63318943977356</v>
       </c>
       <c r="H21" t="n">
-        <v>4.71497368812561</v>
+        <v>4.51399040222168</v>
       </c>
       <c r="I21" t="n">
-        <v>4.431102752685547</v>
+        <v>4.186347723007202</v>
       </c>
       <c r="J21" t="n">
-        <v>4.262115001678467</v>
+        <v>4.515001535415649</v>
       </c>
       <c r="K21" t="n">
-        <v>4.486816167831421</v>
+        <v>4.511001348495483</v>
       </c>
       <c r="L21" t="n">
-        <v>4.410202074050903</v>
+        <v>4.477313876152039</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.071036100387573</v>
+        <v>4.186325073242188</v>
       </c>
       <c r="C22" t="n">
-        <v>3.926327466964722</v>
+        <v>4.182823181152344</v>
       </c>
       <c r="D22" t="n">
-        <v>4.120123386383057</v>
+        <v>4.262640953063965</v>
       </c>
       <c r="E22" t="n">
-        <v>3.961298942565918</v>
+        <v>4.251146078109741</v>
       </c>
       <c r="F22" t="n">
-        <v>4.004124879837036</v>
+        <v>4.18731951713562</v>
       </c>
       <c r="G22" t="n">
-        <v>4.265459775924683</v>
+        <v>4.513005971908569</v>
       </c>
       <c r="H22" t="n">
-        <v>4.113841772079468</v>
+        <v>4.416773557662964</v>
       </c>
       <c r="I22" t="n">
-        <v>3.932161569595337</v>
+        <v>4.425721645355225</v>
       </c>
       <c r="J22" t="n">
-        <v>4.146560907363892</v>
+        <v>4.062162160873413</v>
       </c>
       <c r="K22" t="n">
-        <v>4.015559673309326</v>
+        <v>4.089065074920654</v>
       </c>
       <c r="L22" t="n">
-        <v>4.055649447441101</v>
+        <v>4.257698321342469</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.218665599822998</v>
+        <v>4.314515352249146</v>
       </c>
       <c r="C23" t="n">
-        <v>4.374789476394653</v>
+        <v>4.28560733795166</v>
       </c>
       <c r="D23" t="n">
-        <v>4.103057146072388</v>
+        <v>4.357380867004395</v>
       </c>
       <c r="E23" t="n">
-        <v>3.99958610534668</v>
+        <v>4.226224184036255</v>
       </c>
       <c r="F23" t="n">
-        <v>4.171935319900513</v>
+        <v>4.282597303390503</v>
       </c>
       <c r="G23" t="n">
-        <v>3.975422620773315</v>
+        <v>4.383845329284668</v>
       </c>
       <c r="H23" t="n">
-        <v>4.128450632095337</v>
+        <v>4.37012505531311</v>
       </c>
       <c r="I23" t="n">
-        <v>4.269630432128906</v>
+        <v>4.294302701950073</v>
       </c>
       <c r="J23" t="n">
-        <v>3.864078283309937</v>
+        <v>4.858854293823242</v>
       </c>
       <c r="K23" t="n">
-        <v>4.090043783187866</v>
+        <v>4.482371807098389</v>
       </c>
       <c r="L23" t="n">
-        <v>4.119565939903259</v>
+        <v>4.385582423210144</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4.394892454147339</v>
+        <v>4.522226095199585</v>
       </c>
       <c r="C24" t="n">
-        <v>4.173236846923828</v>
+        <v>4.013564586639404</v>
       </c>
       <c r="D24" t="n">
-        <v>4.302592754364014</v>
+        <v>4.603535652160645</v>
       </c>
       <c r="E24" t="n">
-        <v>3.91128945350647</v>
+        <v>4.223086357116699</v>
       </c>
       <c r="F24" t="n">
-        <v>3.997359037399292</v>
+        <v>4.291815519332886</v>
       </c>
       <c r="G24" t="n">
-        <v>3.935888767242432</v>
+        <v>4.303315877914429</v>
       </c>
       <c r="H24" t="n">
-        <v>3.931029319763184</v>
+        <v>3.981631517410278</v>
       </c>
       <c r="I24" t="n">
-        <v>4.004603624343872</v>
+        <v>4.315266132354736</v>
       </c>
       <c r="J24" t="n">
-        <v>4.268505811691284</v>
+        <v>4.109802722930908</v>
       </c>
       <c r="K24" t="n">
-        <v>3.957086801528931</v>
+        <v>3.949708700180054</v>
       </c>
       <c r="L24" t="n">
-        <v>4.087648487091064</v>
+        <v>4.231395316123963</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>3.854345798492432</v>
+        <v>3.759725093841553</v>
       </c>
       <c r="C25" t="n">
-        <v>3.740304708480835</v>
+        <v>3.934252262115479</v>
       </c>
       <c r="D25" t="n">
-        <v>3.835808515548706</v>
+        <v>3.723383903503418</v>
       </c>
       <c r="E25" t="n">
-        <v>3.845294713973999</v>
+        <v>4.278103590011597</v>
       </c>
       <c r="F25" t="n">
-        <v>3.918548345565796</v>
+        <v>3.888595581054688</v>
       </c>
       <c r="G25" t="n">
-        <v>3.682605504989624</v>
+        <v>3.851742029190063</v>
       </c>
       <c r="H25" t="n">
-        <v>3.814757347106934</v>
+        <v>3.801773309707642</v>
       </c>
       <c r="I25" t="n">
-        <v>3.641576528549194</v>
+        <v>4.236704587936401</v>
       </c>
       <c r="J25" t="n">
-        <v>4.144493818283081</v>
+        <v>4.639180898666382</v>
       </c>
       <c r="K25" t="n">
-        <v>3.669057846069336</v>
+        <v>4.257638931274414</v>
       </c>
       <c r="L25" t="n">
-        <v>3.814679312705993</v>
+        <v>4.037110018730163</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.536577463150024</v>
+        <v>4.695008039474487</v>
       </c>
       <c r="C26" t="n">
-        <v>4.195399284362793</v>
+        <v>4.821223735809326</v>
       </c>
       <c r="D26" t="n">
-        <v>4.351675510406494</v>
+        <v>4.621230840682983</v>
       </c>
       <c r="E26" t="n">
-        <v>4.724021673202515</v>
+        <v>4.701535940170288</v>
       </c>
       <c r="F26" t="n">
-        <v>4.497440338134766</v>
+        <v>4.850634098052979</v>
       </c>
       <c r="G26" t="n">
-        <v>4.428036689758301</v>
+        <v>4.868067026138306</v>
       </c>
       <c r="H26" t="n">
-        <v>4.367735147476196</v>
+        <v>5.199264049530029</v>
       </c>
       <c r="I26" t="n">
-        <v>4.537948369979858</v>
+        <v>4.371877670288086</v>
       </c>
       <c r="J26" t="n">
-        <v>4.61550760269165</v>
+        <v>4.761852979660034</v>
       </c>
       <c r="K26" t="n">
-        <v>4.356816530227661</v>
+        <v>4.574825763702393</v>
       </c>
       <c r="L26" t="n">
-        <v>4.461115860939026</v>
+        <v>4.746552014350891</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>4.444210290908813</v>
+        <v>6.409109354019165</v>
       </c>
       <c r="C27" t="n">
-        <v>4.402653694152832</v>
+        <v>5.013951301574707</v>
       </c>
       <c r="D27" t="n">
-        <v>4.324504613876343</v>
+        <v>4.481502294540405</v>
       </c>
       <c r="E27" t="n">
-        <v>4.757046699523926</v>
+        <v>4.660112857818604</v>
       </c>
       <c r="F27" t="n">
-        <v>4.373804569244385</v>
+        <v>5.165830373764038</v>
       </c>
       <c r="G27" t="n">
-        <v>4.510580778121948</v>
+        <v>5.084039688110352</v>
       </c>
       <c r="H27" t="n">
-        <v>4.350612878799438</v>
+        <v>4.518498420715332</v>
       </c>
       <c r="I27" t="n">
-        <v>5.300443649291992</v>
+        <v>4.824688911437988</v>
       </c>
       <c r="J27" t="n">
-        <v>4.431055784225464</v>
+        <v>5.032171964645386</v>
       </c>
       <c r="K27" t="n">
-        <v>4.605474948883057</v>
+        <v>4.743410348892212</v>
       </c>
       <c r="L27" t="n">
-        <v>4.550038790702819</v>
+        <v>4.993331551551819</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>3.963121652603149</v>
+        <v>4.050162076950073</v>
       </c>
       <c r="C28" t="n">
-        <v>3.923161745071411</v>
+        <v>4.237186193466187</v>
       </c>
       <c r="D28" t="n">
-        <v>4.032205581665039</v>
+        <v>4.453628301620483</v>
       </c>
       <c r="E28" t="n">
-        <v>3.900293827056885</v>
+        <v>4.164875984191895</v>
       </c>
       <c r="F28" t="n">
-        <v>4.746900081634521</v>
+        <v>4.19330620765686</v>
       </c>
       <c r="G28" t="n">
-        <v>4.370819568634033</v>
+        <v>4.487070322036743</v>
       </c>
       <c r="H28" t="n">
-        <v>4.468016624450684</v>
+        <v>4.510005235671997</v>
       </c>
       <c r="I28" t="n">
-        <v>4.02149772644043</v>
+        <v>4.746392011642456</v>
       </c>
       <c r="J28" t="n">
-        <v>4.053621292114258</v>
+        <v>4.747401475906372</v>
       </c>
       <c r="K28" t="n">
-        <v>3.948342323303223</v>
+        <v>4.038249492645264</v>
       </c>
       <c r="L28" t="n">
-        <v>4.142798042297363</v>
+        <v>4.362827730178833</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.195626974105835</v>
+        <v>4.31149959564209</v>
       </c>
       <c r="C29" t="n">
-        <v>4.361193180084229</v>
+        <v>4.173876285552979</v>
       </c>
       <c r="D29" t="n">
-        <v>4.098228931427002</v>
+        <v>4.515573740005493</v>
       </c>
       <c r="E29" t="n">
-        <v>3.975284337997437</v>
+        <v>4.868082761764526</v>
       </c>
       <c r="F29" t="n">
-        <v>4.407536029815674</v>
+        <v>4.249438524246216</v>
       </c>
       <c r="G29" t="n">
-        <v>4.082536697387695</v>
+        <v>4.781075000762939</v>
       </c>
       <c r="H29" t="n">
-        <v>4.120099782943726</v>
+        <v>4.746639490127563</v>
       </c>
       <c r="I29" t="n">
-        <v>3.931555509567261</v>
+        <v>4.468354463577271</v>
       </c>
       <c r="J29" t="n">
-        <v>4.578416109085083</v>
+        <v>4.245439767837524</v>
       </c>
       <c r="K29" t="n">
-        <v>4.021827697753906</v>
+        <v>4.262882947921753</v>
       </c>
       <c r="L29" t="n">
-        <v>4.177230525016784</v>
+        <v>4.462286257743836</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>3.900302171707153</v>
+        <v>4.294314861297607</v>
       </c>
       <c r="C30" t="n">
-        <v>3.964312314987183</v>
+        <v>4.019517183303833</v>
       </c>
       <c r="D30" t="n">
-        <v>4.032513380050659</v>
+        <v>4.130745649337769</v>
       </c>
       <c r="E30" t="n">
-        <v>3.886958360671997</v>
+        <v>4.058932304382324</v>
       </c>
       <c r="F30" t="n">
-        <v>3.710532188415527</v>
+        <v>4.021892786026001</v>
       </c>
       <c r="G30" t="n">
-        <v>3.932760000228882</v>
+        <v>4.087088108062744</v>
       </c>
       <c r="H30" t="n">
-        <v>3.917403221130371</v>
+        <v>4.435701847076416</v>
       </c>
       <c r="I30" t="n">
-        <v>4.126801013946533</v>
+        <v>4.341426134109497</v>
       </c>
       <c r="J30" t="n">
-        <v>4.123319625854492</v>
+        <v>4.289584875106812</v>
       </c>
       <c r="K30" t="n">
-        <v>4.208873987197876</v>
+        <v>4.284570932388306</v>
       </c>
       <c r="L30" t="n">
-        <v>3.980377626419068</v>
+        <v>4.196377468109131</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>4.118225336074829</v>
+        <v>4.098079442977905</v>
       </c>
       <c r="C31" t="n">
-        <v>3.994354248046875</v>
+        <v>4.03570032119751</v>
       </c>
       <c r="D31" t="n">
-        <v>3.830169677734375</v>
+        <v>4.528250455856323</v>
       </c>
       <c r="E31" t="n">
-        <v>3.967454671859741</v>
+        <v>4.050176382064819</v>
       </c>
       <c r="F31" t="n">
-        <v>4.531388998031616</v>
+        <v>4.198299169540405</v>
       </c>
       <c r="G31" t="n">
-        <v>3.759874820709229</v>
+        <v>4.360381364822388</v>
       </c>
       <c r="H31" t="n">
-        <v>3.633929967880249</v>
+        <v>4.130949735641479</v>
       </c>
       <c r="I31" t="n">
-        <v>4.376629829406738</v>
+        <v>4.304594755172729</v>
       </c>
       <c r="J31" t="n">
-        <v>4.125208139419556</v>
+        <v>3.9519362449646</v>
       </c>
       <c r="K31" t="n">
-        <v>3.819345951080322</v>
+        <v>4.402766227722168</v>
       </c>
       <c r="L31" t="n">
-        <v>4.015658164024353</v>
+        <v>4.206113409996033</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>4.035204172134399</v>
+        <v>4.197337627410889</v>
       </c>
       <c r="C32" t="n">
-        <v>3.938362598419189</v>
+        <v>4.000784158706665</v>
       </c>
       <c r="D32" t="n">
-        <v>4.163842916488647</v>
+        <v>3.89806604385376</v>
       </c>
       <c r="E32" t="n">
-        <v>4.13742733001709</v>
+        <v>4.050187110900879</v>
       </c>
       <c r="F32" t="n">
-        <v>3.649368524551392</v>
+        <v>4.555867671966553</v>
       </c>
       <c r="G32" t="n">
-        <v>4.006908893585205</v>
+        <v>3.88860034942627</v>
       </c>
       <c r="H32" t="n">
-        <v>3.80085563659668</v>
+        <v>4.002780675888062</v>
       </c>
       <c r="I32" t="n">
-        <v>4.031548976898193</v>
+        <v>3.740976095199585</v>
       </c>
       <c r="J32" t="n">
-        <v>3.938668966293335</v>
+        <v>3.943940877914429</v>
       </c>
       <c r="K32" t="n">
-        <v>3.794396877288818</v>
+        <v>4.550891876220703</v>
       </c>
       <c r="L32" t="n">
-        <v>3.949658489227295</v>
+        <v>4.082943248748779</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.593537569046021</v>
+        <v>4.613277673721313</v>
       </c>
       <c r="C33" t="n">
-        <v>4.118840217590332</v>
+        <v>4.653130054473877</v>
       </c>
       <c r="D33" t="n">
-        <v>4.228758096694946</v>
+        <v>5.005260705947876</v>
       </c>
       <c r="E33" t="n">
-        <v>4.187680244445801</v>
+        <v>4.274598360061646</v>
       </c>
       <c r="F33" t="n">
-        <v>4.261226415634155</v>
+        <v>4.854639291763306</v>
       </c>
       <c r="G33" t="n">
-        <v>4.446006059646606</v>
+        <v>4.67657470703125</v>
       </c>
       <c r="H33" t="n">
-        <v>4.251066207885742</v>
+        <v>4.465619564056396</v>
       </c>
       <c r="I33" t="n">
-        <v>4.48774266242981</v>
+        <v>4.367855072021484</v>
       </c>
       <c r="J33" t="n">
-        <v>4.451172351837158</v>
+        <v>4.17682957649231</v>
       </c>
       <c r="K33" t="n">
-        <v>4.021489143371582</v>
+        <v>4.372862577438354</v>
       </c>
       <c r="L33" t="n">
-        <v>4.304751896858216</v>
+        <v>4.546064758300782</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>3.653540134429932</v>
+        <v>3.769381284713745</v>
       </c>
       <c r="C34" t="n">
-        <v>3.603217363357544</v>
+        <v>3.880112886428833</v>
       </c>
       <c r="D34" t="n">
-        <v>3.549089908599854</v>
+        <v>3.691084384918213</v>
       </c>
       <c r="E34" t="n">
-        <v>3.675473690032959</v>
+        <v>3.956911325454712</v>
       </c>
       <c r="F34" t="n">
-        <v>3.72253942489624</v>
+        <v>3.830237865447998</v>
       </c>
       <c r="G34" t="n">
-        <v>3.466687679290771</v>
+        <v>3.911519289016724</v>
       </c>
       <c r="H34" t="n">
-        <v>3.639006614685059</v>
+        <v>3.849179267883301</v>
       </c>
       <c r="I34" t="n">
-        <v>3.694109201431274</v>
+        <v>3.88261079788208</v>
       </c>
       <c r="J34" t="n">
-        <v>3.604340553283691</v>
+        <v>3.793332815170288</v>
       </c>
       <c r="K34" t="n">
-        <v>3.754384994506836</v>
+        <v>3.860677480697632</v>
       </c>
       <c r="L34" t="n">
-        <v>3.636238956451416</v>
+        <v>3.842504739761353</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>4.945902109146118</v>
+        <v>5.061086893081665</v>
       </c>
       <c r="C35" t="n">
-        <v>6.068828582763672</v>
+        <v>4.954394340515137</v>
       </c>
       <c r="D35" t="n">
-        <v>4.886919498443604</v>
+        <v>5.900949001312256</v>
       </c>
       <c r="E35" t="n">
-        <v>4.630179405212402</v>
+        <v>4.693537712097168</v>
       </c>
       <c r="F35" t="n">
-        <v>4.881918907165527</v>
+        <v>5.124441862106323</v>
       </c>
       <c r="G35" t="n">
-        <v>5.11190390586853</v>
+        <v>4.989311456680298</v>
       </c>
       <c r="H35" t="n">
-        <v>4.516042232513428</v>
+        <v>5.118427276611328</v>
       </c>
       <c r="I35" t="n">
-        <v>4.648434638977051</v>
+        <v>4.841168165206909</v>
       </c>
       <c r="J35" t="n">
-        <v>5.010587453842163</v>
+        <v>5.163331747055054</v>
       </c>
       <c r="K35" t="n">
-        <v>4.397490739822388</v>
+        <v>5.489675521850586</v>
       </c>
       <c r="L35" t="n">
-        <v>4.909820747375488</v>
+        <v>5.133632397651672</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>3.521898984909058</v>
+        <v>3.652668476104736</v>
       </c>
       <c r="C36" t="n">
-        <v>3.451264142990112</v>
+        <v>4.062154293060303</v>
       </c>
       <c r="D36" t="n">
-        <v>3.441388845443726</v>
+        <v>3.685113191604614</v>
       </c>
       <c r="E36" t="n">
-        <v>3.668980121612549</v>
+        <v>3.722004413604736</v>
       </c>
       <c r="F36" t="n">
-        <v>3.517323017120361</v>
+        <v>3.561428785324097</v>
       </c>
       <c r="G36" t="n">
-        <v>3.373486042022705</v>
+        <v>3.672149181365967</v>
       </c>
       <c r="H36" t="n">
-        <v>3.508975744247437</v>
+        <v>3.587851285934448</v>
       </c>
       <c r="I36" t="n">
-        <v>3.695724487304688</v>
+        <v>3.671627521514893</v>
       </c>
       <c r="J36" t="n">
-        <v>3.558720827102661</v>
+        <v>3.960899353027344</v>
       </c>
       <c r="K36" t="n">
-        <v>3.560246706008911</v>
+        <v>3.62474513053894</v>
       </c>
       <c r="L36" t="n">
-        <v>3.529800891876221</v>
+        <v>3.720064163208008</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>4.160633325576782</v>
+        <v>4.983322858810425</v>
       </c>
       <c r="C37" t="n">
-        <v>4.424185752868652</v>
+        <v>5.03425669670105</v>
       </c>
       <c r="D37" t="n">
-        <v>4.135822296142578</v>
+        <v>4.774822235107422</v>
       </c>
       <c r="E37" t="n">
-        <v>4.235689163208008</v>
+        <v>4.303531646728516</v>
       </c>
       <c r="F37" t="n">
-        <v>4.102447509765625</v>
+        <v>4.634209632873535</v>
       </c>
       <c r="G37" t="n">
-        <v>4.301820278167725</v>
+        <v>4.606274843215942</v>
       </c>
       <c r="H37" t="n">
-        <v>4.512127637863159</v>
+        <v>4.948901414871216</v>
       </c>
       <c r="I37" t="n">
-        <v>4.566266298294067</v>
+        <v>4.565383434295654</v>
       </c>
       <c r="J37" t="n">
-        <v>4.647275447845459</v>
+        <v>4.778812170028687</v>
       </c>
       <c r="K37" t="n">
-        <v>4.216228246688843</v>
+        <v>4.68804407119751</v>
       </c>
       <c r="L37" t="n">
-        <v>4.33024959564209</v>
+        <v>4.731755900382995</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>4.218990087509155</v>
+        <v>4.732924222946167</v>
       </c>
       <c r="C38" t="n">
-        <v>4.243429660797119</v>
+        <v>4.533951997756958</v>
       </c>
       <c r="D38" t="n">
-        <v>4.393421649932861</v>
+        <v>4.387812376022339</v>
       </c>
       <c r="E38" t="n">
-        <v>4.326608419418335</v>
+        <v>4.359395503997803</v>
       </c>
       <c r="F38" t="n">
-        <v>3.997336626052856</v>
+        <v>4.412744998931885</v>
       </c>
       <c r="G38" t="n">
-        <v>4.164775609970093</v>
+        <v>4.428691387176514</v>
       </c>
       <c r="H38" t="n">
-        <v>4.360890865325928</v>
+        <v>4.356913566589355</v>
       </c>
       <c r="I38" t="n">
-        <v>4.578470706939697</v>
+        <v>4.256136178970337</v>
       </c>
       <c r="J38" t="n">
-        <v>5.27053689956665</v>
+        <v>4.545459985733032</v>
       </c>
       <c r="K38" t="n">
-        <v>4.256943941116333</v>
+        <v>4.543917894363403</v>
       </c>
       <c r="L38" t="n">
-        <v>4.381140446662902</v>
+        <v>4.455794811248779</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>3.794103622436523</v>
+        <v>3.936462163925171</v>
       </c>
       <c r="C39" t="n">
-        <v>3.794196605682373</v>
+        <v>4.148424386978149</v>
       </c>
       <c r="D39" t="n">
-        <v>3.758983850479126</v>
+        <v>3.996800422668457</v>
       </c>
       <c r="E39" t="n">
-        <v>4.071263313293457</v>
+        <v>4.052677154541016</v>
       </c>
       <c r="F39" t="n">
-        <v>3.592155694961548</v>
+        <v>3.69605827331543</v>
       </c>
       <c r="G39" t="n">
-        <v>3.801976680755615</v>
+        <v>3.947773694992065</v>
       </c>
       <c r="H39" t="n">
-        <v>4.268771886825562</v>
+        <v>3.909316539764404</v>
       </c>
       <c r="I39" t="n">
-        <v>3.819552898406982</v>
+        <v>4.128287553787231</v>
       </c>
       <c r="J39" t="n">
-        <v>3.905926704406738</v>
+        <v>3.980145454406738</v>
       </c>
       <c r="K39" t="n">
-        <v>3.520229816436768</v>
+        <v>3.758201599121094</v>
       </c>
       <c r="L39" t="n">
-        <v>3.832716107368469</v>
+        <v>3.955414724349976</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.30077052116394</v>
+        <v>4.582567930221558</v>
       </c>
       <c r="C40" t="n">
-        <v>4.111124753952026</v>
+        <v>4.370111703872681</v>
       </c>
       <c r="D40" t="n">
-        <v>4.129146575927734</v>
+        <v>4.649382352828979</v>
       </c>
       <c r="E40" t="n">
-        <v>4.276830673217773</v>
+        <v>4.649962663650513</v>
       </c>
       <c r="F40" t="n">
-        <v>4.183069944381714</v>
+        <v>4.381577730178833</v>
       </c>
       <c r="G40" t="n">
-        <v>4.412467241287231</v>
+        <v>4.724221229553223</v>
       </c>
       <c r="H40" t="n">
-        <v>4.5989830493927</v>
+        <v>4.579067468643188</v>
       </c>
       <c r="I40" t="n">
-        <v>4.496735095977783</v>
+        <v>4.682799100875854</v>
       </c>
       <c r="J40" t="n">
-        <v>4.389189481735229</v>
+        <v>4.454928636550903</v>
       </c>
       <c r="K40" t="n">
-        <v>4.244843006134033</v>
+        <v>4.346177577972412</v>
       </c>
       <c r="L40" t="n">
-        <v>4.314316034317017</v>
+        <v>4.542079639434815</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.131032705307007</v>
+        <v>4.991048336029053</v>
       </c>
       <c r="C41" t="n">
-        <v>4.335487842559814</v>
+        <v>4.401536226272583</v>
       </c>
       <c r="D41" t="n">
-        <v>4.279677391052246</v>
+        <v>4.265405893325806</v>
       </c>
       <c r="E41" t="n">
-        <v>4.043838500976562</v>
+        <v>4.441440105438232</v>
       </c>
       <c r="F41" t="n">
-        <v>4.137953281402588</v>
+        <v>4.900727987289429</v>
       </c>
       <c r="G41" t="n">
-        <v>4.033078193664551</v>
+        <v>4.662873029708862</v>
       </c>
       <c r="H41" t="n">
-        <v>4.095422506332397</v>
+        <v>4.82844090461731</v>
       </c>
       <c r="I41" t="n">
-        <v>4.121082305908203</v>
+        <v>4.256408929824829</v>
       </c>
       <c r="J41" t="n">
-        <v>4.132939577102661</v>
+        <v>4.388557910919189</v>
       </c>
       <c r="K41" t="n">
-        <v>4.527926683425903</v>
+        <v>4.340198278427124</v>
       </c>
       <c r="L41" t="n">
-        <v>4.183843898773193</v>
+        <v>4.547663760185242</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>4.497247695922852</v>
+        <v>4.368618726730347</v>
       </c>
       <c r="C42" t="n">
-        <v>4.473479986190796</v>
+        <v>4.4444580078125</v>
       </c>
       <c r="D42" t="n">
-        <v>4.128484487533569</v>
+        <v>4.016557216644287</v>
       </c>
       <c r="E42" t="n">
-        <v>3.975166797637939</v>
+        <v>4.738157510757446</v>
       </c>
       <c r="F42" t="n">
-        <v>3.967828035354614</v>
+        <v>4.6793372631073</v>
       </c>
       <c r="G42" t="n">
-        <v>3.934999704360962</v>
+        <v>4.308269739151001</v>
       </c>
       <c r="H42" t="n">
-        <v>3.92899751663208</v>
+        <v>4.214044570922852</v>
       </c>
       <c r="I42" t="n">
-        <v>4.000639677047729</v>
+        <v>4.79053258895874</v>
       </c>
       <c r="J42" t="n">
-        <v>4.334621667861938</v>
+        <v>4.123770713806152</v>
       </c>
       <c r="K42" t="n">
-        <v>4.43305778503418</v>
+        <v>4.53866720199585</v>
       </c>
       <c r="L42" t="n">
-        <v>4.167452335357666</v>
+        <v>4.422241353988648</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.08740496635437</v>
+        <v>4.631460905075073</v>
       </c>
       <c r="C43" t="n">
-        <v>4.306639194488525</v>
+        <v>4.69519567489624</v>
       </c>
       <c r="D43" t="n">
-        <v>4.131828308105469</v>
+        <v>4.577362775802612</v>
       </c>
       <c r="E43" t="n">
-        <v>4.075999736785889</v>
+        <v>4.493064880371094</v>
       </c>
       <c r="F43" t="n">
-        <v>4.43817925453186</v>
+        <v>4.650157928466797</v>
       </c>
       <c r="G43" t="n">
-        <v>4.341223955154419</v>
+        <v>4.460128545761108</v>
       </c>
       <c r="H43" t="n">
-        <v>4.473613262176514</v>
+        <v>4.304593086242676</v>
       </c>
       <c r="I43" t="n">
-        <v>4.501002788543701</v>
+        <v>4.648148775100708</v>
       </c>
       <c r="J43" t="n">
-        <v>4.360012531280518</v>
+        <v>4.768526077270508</v>
       </c>
       <c r="K43" t="n">
-        <v>4.32546067237854</v>
+        <v>4.666845798492432</v>
       </c>
       <c r="L43" t="n">
-        <v>4.304136466979981</v>
+        <v>4.589548444747924</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>3.844536542892456</v>
+        <v>4.158654451370239</v>
       </c>
       <c r="C44" t="n">
-        <v>3.961910963058472</v>
+        <v>4.486806631088257</v>
       </c>
       <c r="D44" t="n">
-        <v>4.056383371353149</v>
+        <v>4.338201284408569</v>
       </c>
       <c r="E44" t="n">
-        <v>4.178241968154907</v>
+        <v>4.080899477005005</v>
       </c>
       <c r="F44" t="n">
-        <v>3.894717216491699</v>
+        <v>4.229987382888794</v>
       </c>
       <c r="G44" t="n">
-        <v>3.83231782913208</v>
+        <v>4.246459007263184</v>
       </c>
       <c r="H44" t="n">
-        <v>3.874117851257324</v>
+        <v>4.285846948623657</v>
       </c>
       <c r="I44" t="n">
-        <v>3.972565174102783</v>
+        <v>4.865841388702393</v>
       </c>
       <c r="J44" t="n">
-        <v>4.141317844390869</v>
+        <v>4.536678552627563</v>
       </c>
       <c r="K44" t="n">
-        <v>4.196433782577515</v>
+        <v>4.311277866363525</v>
       </c>
       <c r="L44" t="n">
-        <v>3.995254254341126</v>
+        <v>4.354065299034119</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>4.112533092498779</v>
+        <v>3.922291994094849</v>
       </c>
       <c r="C45" t="n">
-        <v>3.752319097518921</v>
+        <v>4.256426334381104</v>
       </c>
       <c r="D45" t="n">
-        <v>3.921895503997803</v>
+        <v>3.960182189941406</v>
       </c>
       <c r="E45" t="n">
-        <v>3.743486166000366</v>
+        <v>4.319743871688843</v>
       </c>
       <c r="F45" t="n">
-        <v>3.739984273910522</v>
+        <v>4.017537593841553</v>
       </c>
       <c r="G45" t="n">
-        <v>3.938568353652954</v>
+        <v>4.242943525314331</v>
       </c>
       <c r="H45" t="n">
-        <v>3.81190299987793</v>
+        <v>4.15069317817688</v>
       </c>
       <c r="I45" t="n">
-        <v>3.876505613327026</v>
+        <v>4.174144983291626</v>
       </c>
       <c r="J45" t="n">
-        <v>3.97950291633606</v>
+        <v>4.190724849700928</v>
       </c>
       <c r="K45" t="n">
-        <v>4.059245824813843</v>
+        <v>3.984639883041382</v>
       </c>
       <c r="L45" t="n">
-        <v>3.89359438419342</v>
+        <v>4.12193284034729</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.134292602539062</v>
+        <v>4.271863698959351</v>
       </c>
       <c r="C46" t="n">
-        <v>4.436702013015747</v>
+        <v>4.0359947681427</v>
       </c>
       <c r="D46" t="n">
-        <v>3.859107971191406</v>
+        <v>4.237970590591431</v>
       </c>
       <c r="E46" t="n">
-        <v>3.950732946395874</v>
+        <v>4.76109504699707</v>
       </c>
       <c r="F46" t="n">
-        <v>4.129573345184326</v>
+        <v>4.278349637985229</v>
       </c>
       <c r="G46" t="n">
-        <v>4.223772764205933</v>
+        <v>4.273386478424072</v>
       </c>
       <c r="H46" t="n">
-        <v>3.783159017562866</v>
+        <v>4.609991550445557</v>
       </c>
       <c r="I46" t="n">
-        <v>4.008785009384155</v>
+        <v>4.418534517288208</v>
       </c>
       <c r="J46" t="n">
-        <v>4.327162504196167</v>
+        <v>4.704253196716309</v>
       </c>
       <c r="K46" t="n">
-        <v>4.293460130691528</v>
+        <v>4.123096942901611</v>
       </c>
       <c r="L46" t="n">
-        <v>4.114674830436707</v>
+        <v>4.371453642845154</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.686814546585083</v>
+        <v>4.864102602005005</v>
       </c>
       <c r="C47" t="n">
-        <v>4.484146356582642</v>
+        <v>4.51699686050415</v>
       </c>
       <c r="D47" t="n">
-        <v>4.450339555740356</v>
+        <v>4.512983798980713</v>
       </c>
       <c r="E47" t="n">
-        <v>5.057795286178589</v>
+        <v>4.923941612243652</v>
       </c>
       <c r="F47" t="n">
-        <v>4.636558532714844</v>
+        <v>4.196295976638794</v>
       </c>
       <c r="G47" t="n">
-        <v>4.075479745864868</v>
+        <v>4.063632726669312</v>
       </c>
       <c r="H47" t="n">
-        <v>4.022576332092285</v>
+        <v>4.489073514938354</v>
       </c>
       <c r="I47" t="n">
-        <v>4.099411249160767</v>
+        <v>4.706506013870239</v>
       </c>
       <c r="J47" t="n">
-        <v>4.467857360839844</v>
+        <v>5.123445749282837</v>
       </c>
       <c r="K47" t="n">
-        <v>4.115689277648926</v>
+        <v>4.183362245559692</v>
       </c>
       <c r="L47" t="n">
-        <v>4.40966682434082</v>
+        <v>4.558034110069275</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.296870470046997</v>
+        <v>4.109034061431885</v>
       </c>
       <c r="C48" t="n">
-        <v>4.17774224281311</v>
+        <v>4.428730487823486</v>
       </c>
       <c r="D48" t="n">
-        <v>4.456450462341309</v>
+        <v>4.441203355789185</v>
       </c>
       <c r="E48" t="n">
-        <v>3.882418632507324</v>
+        <v>4.202765703201294</v>
       </c>
       <c r="F48" t="n">
-        <v>4.254580974578857</v>
+        <v>4.323008060455322</v>
       </c>
       <c r="G48" t="n">
-        <v>4.417313814163208</v>
+        <v>4.230194330215454</v>
       </c>
       <c r="H48" t="n">
-        <v>4.013531684875488</v>
+        <v>4.804769515991211</v>
       </c>
       <c r="I48" t="n">
-        <v>4.344815969467163</v>
+        <v>4.733423948287964</v>
       </c>
       <c r="J48" t="n">
-        <v>4.344052791595459</v>
+        <v>4.530963182449341</v>
       </c>
       <c r="K48" t="n">
-        <v>4.313913822174072</v>
+        <v>4.105055093765259</v>
       </c>
       <c r="L48" t="n">
-        <v>4.250169086456299</v>
+        <v>4.39091477394104</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>4.139932155609131</v>
+        <v>4.569332599639893</v>
       </c>
       <c r="C49" t="n">
-        <v>3.975824356079102</v>
+        <v>4.468615293502808</v>
       </c>
       <c r="D49" t="n">
-        <v>4.52301812171936</v>
+        <v>4.463123083114624</v>
       </c>
       <c r="E49" t="n">
-        <v>4.723172903060913</v>
+        <v>4.738430976867676</v>
       </c>
       <c r="F49" t="n">
-        <v>4.667860269546509</v>
+        <v>4.627196311950684</v>
       </c>
       <c r="G49" t="n">
-        <v>4.388294696807861</v>
+        <v>4.779797554016113</v>
       </c>
       <c r="H49" t="n">
-        <v>4.138365983963013</v>
+        <v>4.503058671951294</v>
       </c>
       <c r="I49" t="n">
-        <v>4.23263955116272</v>
+        <v>4.800786733627319</v>
       </c>
       <c r="J49" t="n">
-        <v>4.599614858627319</v>
+        <v>4.495041608810425</v>
       </c>
       <c r="K49" t="n">
-        <v>4.008845567703247</v>
+        <v>5.451102733612061</v>
       </c>
       <c r="L49" t="n">
-        <v>4.339756846427917</v>
+        <v>4.689648556709289</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.418848276138306</v>
+        <v>3.540979862213135</v>
       </c>
       <c r="C50" t="n">
-        <v>3.60819673538208</v>
+        <v>3.758902788162231</v>
       </c>
       <c r="D50" t="n">
-        <v>3.380910396575928</v>
+        <v>4.026729345321655</v>
       </c>
       <c r="E50" t="n">
-        <v>3.684934139251709</v>
+        <v>4.063137531280518</v>
       </c>
       <c r="F50" t="n">
-        <v>3.424418687820435</v>
+        <v>3.60779333114624</v>
       </c>
       <c r="G50" t="n">
-        <v>3.429854393005371</v>
+        <v>3.68012261390686</v>
       </c>
       <c r="H50" t="n">
-        <v>3.714736461639404</v>
+        <v>3.491097450256348</v>
       </c>
       <c r="I50" t="n">
-        <v>3.514944314956665</v>
+        <v>3.623264789581299</v>
       </c>
       <c r="J50" t="n">
-        <v>3.469030618667603</v>
+        <v>3.647707462310791</v>
       </c>
       <c r="K50" t="n">
-        <v>3.582929134368896</v>
+        <v>3.603801012039185</v>
       </c>
       <c r="L50" t="n">
-        <v>3.52288031578064</v>
+        <v>3.704353618621826</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.15611743927002</v>
+        <v>4.364377737045288</v>
       </c>
       <c r="C51" t="n">
-        <v>3.978575229644775</v>
+        <v>4.682559251785278</v>
       </c>
       <c r="D51" t="n">
-        <v>4.15851092338562</v>
+        <v>4.51499080657959</v>
       </c>
       <c r="E51" t="n">
-        <v>4.171812534332275</v>
+        <v>4.436195373535156</v>
       </c>
       <c r="F51" t="n">
-        <v>4.090543508529663</v>
+        <v>4.170846939086914</v>
       </c>
       <c r="G51" t="n">
-        <v>4.131022930145264</v>
+        <v>4.464115381240845</v>
       </c>
       <c r="H51" t="n">
-        <v>4.053396463394165</v>
+        <v>4.381327629089355</v>
       </c>
       <c r="I51" t="n">
-        <v>4.221600294113159</v>
+        <v>4.171380996704102</v>
       </c>
       <c r="J51" t="n">
-        <v>3.968487501144409</v>
+        <v>4.423725366592407</v>
       </c>
       <c r="K51" t="n">
-        <v>4.335078001022339</v>
+        <v>4.927954912185669</v>
       </c>
       <c r="L51" t="n">
-        <v>4.126514482498169</v>
+        <v>4.45374743938446</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.279654288291932</v>
+        <v>4.375069890022278</v>
       </c>
       <c r="C52" t="n">
-        <v>4.274767818450928</v>
+        <v>4.357887263298035</v>
       </c>
       <c r="D52" t="n">
-        <v>4.25156919002533</v>
+        <v>4.387276182174682</v>
       </c>
       <c r="E52" t="n">
-        <v>4.30646876335144</v>
+        <v>4.390843305587769</v>
       </c>
       <c r="F52" t="n">
-        <v>4.305882906913757</v>
+        <v>4.376153798103332</v>
       </c>
       <c r="G52" t="n">
-        <v>4.218314361572266</v>
+        <v>4.412958216667175</v>
       </c>
       <c r="H52" t="n">
-        <v>4.197924489974976</v>
+        <v>4.423469910621643</v>
       </c>
       <c r="I52" t="n">
-        <v>4.286819934844971</v>
+        <v>4.392616291046142</v>
       </c>
       <c r="J52" t="n">
-        <v>4.313714375495911</v>
+        <v>4.421206340789795</v>
       </c>
       <c r="K52" t="n">
-        <v>4.204047899246216</v>
+        <v>4.369125366210938</v>
       </c>
       <c r="L52" t="n">
-        <v>4.263916402816773</v>
+        <v>4.390660656452179</v>
       </c>
     </row>
   </sheetData>
